--- a/myprojects/GUJTLRM/Gujarat_Toolroom_Investment_Analysis.xlsx
+++ b/myprojects/GUJTLRM/Gujarat_Toolroom_Investment_Analysis.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="450" windowWidth="21570" windowHeight="9435" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="900" windowWidth="21570" windowHeight="9435" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="HOME" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="292">
   <si>
     <t>GUJARAT TOOLROOM LIMITED</t>
   </si>
@@ -566,9 +566,6 @@
     <t>How much revenue is generated per ₹1 of working capital. FY25 fell as working capital surged.</t>
   </si>
   <si>
-    <t>EPS — Earnings Per Share (₹)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> pat ÷ Weighted Avg Shares</t>
   </si>
   <si>
@@ -576,9 +573,6 @@
   </si>
   <si>
     <t>Book Value Per Share (₹)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> total equity ÷ No. of Shares (in Lakhs, scaled)</t>
   </si>
   <si>
     <t>What each share is 'worth' on the books (assets minus liabilities). FY25 higher due to new equity raised.</t>
@@ -798,9 +792,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Divident Paid</t>
-  </si>
-  <si>
     <t>Direct Tax Paid &amp; Other Adj.</t>
   </si>
   <si>
@@ -913,6 +904,18 @@
   </si>
   <si>
     <t>A Qualified Institutional Placement (QIP) is a capital-raising tool used primarily in India, allowing listed companies to raise funds by issuing equity shares or convertible securities exclusively to Qualified Institutional Buyers (QIBs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> total equity ÷ No. of Shares (in Lakhs)</t>
+  </si>
+  <si>
+    <t>EPS - Earnings Per Share (₹)</t>
+  </si>
+  <si>
+    <t>Dividend Paid</t>
+  </si>
+  <si>
+    <t>FY24 Purchases exceeded Revenue because the company was building up inventory (Change in Inventories = -₹6,010 Lakhs). The excess purchases went into closing stock, not sales.</t>
   </si>
 </sst>
 </file>
@@ -923,7 +926,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00;\(#,##0.00\);\-"/>
     <numFmt numFmtId="165" formatCode="0.00%;\(0.00%\);\-"/>
     <numFmt numFmtId="166" formatCode="0.00;\(0.00\);\-"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="37" x14ac:knownFonts="1">
     <font>
@@ -1280,47 +1283,8 @@
     <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1507,60 +1471,15 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1571,37 +1490,122 @@
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="25" fillId="12" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="13" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="12" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="12" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="35" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="30" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="13" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="12" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1874,366 +1878,366 @@
   <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" style="14" customWidth="1"/>
-    <col min="2" max="2" width="26" style="14" customWidth="1"/>
-    <col min="3" max="3" width="22" style="14" customWidth="1"/>
-    <col min="4" max="4" width="35" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="18" style="14" customWidth="1"/>
-    <col min="9" max="9" width="4" style="14" customWidth="1"/>
+    <col min="1" max="1" width="4" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="1" customWidth="1"/>
+    <col min="4" max="4" width="35" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="18" style="1" customWidth="1"/>
+    <col min="9" max="9" width="4" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
     </row>
     <row r="2" spans="2:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
     </row>
     <row r="3" spans="2:8" ht="6.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
     </row>
     <row r="4" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
     </row>
     <row r="5" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="97" t="s">
+      <c r="B5" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
     </row>
     <row r="7" spans="2:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="104" t="s">
-        <v>277</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
+      <c r="B7" s="97" t="s">
+        <v>274</v>
+      </c>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
     </row>
     <row r="8" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="93" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+    </row>
+    <row r="9" spans="2:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="92"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+    </row>
+    <row r="10" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="92" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="92"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="92"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+    </row>
+    <row r="12" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+    </row>
+    <row r="13" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+    </row>
+    <row r="14" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="91" t="s">
+        <v>248</v>
+      </c>
+      <c r="C14" s="91"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="91"/>
+    </row>
+    <row r="15" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="91" t="s">
         <v>247</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-    </row>
-    <row r="9" spans="2:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
+      <c r="C15" s="91"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="91"/>
+    </row>
+    <row r="16" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="91" t="s">
         <v>246</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-    </row>
-    <row r="15" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-    </row>
-    <row r="16" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="91"/>
+      <c r="G16" s="91"/>
+      <c r="H16" s="91"/>
     </row>
     <row r="17" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="91"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="91"/>
+      <c r="H18" s="91"/>
     </row>
     <row r="19" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="105" t="s">
+      <c r="B19" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
     </row>
     <row r="20" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="88"/>
     </row>
     <row r="21" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="95" t="s">
+      <c r="B21" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="95"/>
-      <c r="D21" s="95"/>
-      <c r="E21" s="95"/>
-      <c r="F21" s="95"/>
-      <c r="G21" s="95"/>
-      <c r="H21" s="95"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="89"/>
+      <c r="G21" s="89"/>
+      <c r="H21" s="89"/>
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="15" t="s">
+      <c r="C22" s="90"/>
+      <c r="D22" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="16" t="s">
+      <c r="C23" s="83"/>
+      <c r="D23" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="17" t="s">
+      <c r="C24" s="84"/>
+      <c r="D24" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="16" t="s">
+      <c r="C25" s="83"/>
+      <c r="D25" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="17" t="s">
+      <c r="C26" s="84"/>
+      <c r="D26" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="16" t="s">
+      <c r="C27" s="83"/>
+      <c r="D27" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="17" t="s">
+      <c r="C28" s="84"/>
+      <c r="D28" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="16" t="s">
+      <c r="C29" s="83"/>
+      <c r="D29" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="17" t="s">
+      <c r="C30" s="84"/>
+      <c r="D30" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="16" t="s">
+      <c r="C31" s="83"/>
+      <c r="D31" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="17" t="s">
+      <c r="C32" s="84"/>
+      <c r="D32" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="92"/>
-      <c r="B34" s="92"/>
-      <c r="C34" s="92"/>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="92"/>
-      <c r="G34" s="92"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="92"/>
+      <c r="A34" s="85"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="85"/>
+      <c r="G34" s="85"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B1:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="A34:I34"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B1:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B8:H8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2245,11 +2249,11 @@
   <dimension ref="A1:W83"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" style="14" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" style="14" customWidth="1"/>
-    <col min="4" max="5" width="18" style="14" customWidth="1"/>
-    <col min="6" max="6" width="4" style="14" customWidth="1"/>
+    <col min="1" max="1" width="3" style="1" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" style="1" customWidth="1"/>
+    <col min="4" max="5" width="18" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4" style="1" customWidth="1"/>
     <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -2268,2567 +2272,2543 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="100" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="G1" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="100" t="s">
+        <v>257</v>
+      </c>
+      <c r="N1" s="100"/>
+      <c r="O1" s="100"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="100"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="99" t="s">
+        <v>268</v>
+      </c>
+      <c r="T1" s="100"/>
+      <c r="U1" s="100"/>
+      <c r="V1" s="100"/>
+      <c r="W1" s="100"/>
+    </row>
+    <row r="2" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="100"/>
+      <c r="T2" s="100"/>
+      <c r="U2" s="100"/>
+      <c r="V2" s="100"/>
+      <c r="W2" s="100"/>
+    </row>
+    <row r="3" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="102" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="85"/>
+      <c r="T3" s="85"/>
+      <c r="U3" s="85"/>
+      <c r="V3" s="85"/>
+      <c r="W3" s="85"/>
+    </row>
+    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+    </row>
+    <row r="5" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="90" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="G5" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="94" t="s">
-        <v>271</v>
-      </c>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-    </row>
-    <row r="2" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-    </row>
-    <row r="3" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="80" t="s">
-        <v>263</v>
-      </c>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="92"/>
-      <c r="T3" s="92"/>
-      <c r="U3" s="92"/>
-      <c r="V3" s="92"/>
-      <c r="W3" s="92"/>
-    </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="G4" s="92"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="92"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-    </row>
-    <row r="5" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="G5" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="95" t="s">
-        <v>278</v>
-      </c>
-      <c r="T5" s="81"/>
-      <c r="U5" s="81"/>
-      <c r="V5" s="81"/>
-      <c r="W5" s="81"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="89" t="s">
+        <v>275</v>
+      </c>
+      <c r="T5" s="101"/>
+      <c r="U5" s="101"/>
+      <c r="V5" s="101"/>
+      <c r="W5" s="101"/>
     </row>
     <row r="6" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L6" s="14"/>
-      <c r="M6" s="15" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N6" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O6" s="15" t="s">
+      <c r="N6" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="P6" s="15" t="s">
+      <c r="P6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q6" s="15" t="s">
+      <c r="Q6" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="R6" s="14"/>
-      <c r="S6" s="15" t="s">
+      <c r="R6" s="1"/>
+      <c r="S6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="T6" s="15" t="s">
+      <c r="T6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="U6" s="15" t="s">
+      <c r="U6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V6" s="15" t="s">
+      <c r="V6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="W6" s="15" t="s">
+      <c r="W6" s="2" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="7" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="20">
+      <c r="C7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="7">
         <v>31379.09</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="7">
         <v>20590.29</v>
       </c>
-      <c r="F7" s="21"/>
-      <c r="G7" s="34" t="s">
+      <c r="F7" s="8"/>
+      <c r="G7" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="23">
         <f>D7</f>
         <v>31379.09</v>
       </c>
-      <c r="J7" s="36">
+      <c r="J7" s="23">
         <f>E7</f>
         <v>20590.29</v>
       </c>
-      <c r="K7" s="91">
+      <c r="K7" s="67">
         <f>(I7-J7)/J7</f>
         <v>0.52397513585287037</v>
       </c>
-      <c r="L7" s="14"/>
-      <c r="M7" s="34" t="s">
+      <c r="L7" s="1"/>
+      <c r="M7" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="N7" s="49" t="s">
+      <c r="N7" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="O7" s="37">
+      <c r="O7" s="24">
         <f>I16</f>
         <v>3.7014457716906389E-2</v>
       </c>
-      <c r="P7" s="37">
+      <c r="P7" s="24">
         <f>J16</f>
         <v>6.1274027709177482E-2</v>
       </c>
-      <c r="Q7" s="50" t="s">
+      <c r="Q7" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="R7" s="14"/>
-      <c r="S7" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="T7" s="19" t="s">
+      <c r="R7" s="1"/>
+      <c r="S7" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="T7" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="U7" s="56">
+      <c r="U7" s="43">
         <f>D36</f>
         <v>54502.829999999994</v>
       </c>
-      <c r="V7" s="56">
+      <c r="V7" s="43">
         <f>E36</f>
         <v>9830.83</v>
       </c>
-      <c r="W7" s="59">
+      <c r="W7" s="46">
         <f>U7-V7</f>
         <v>44671.999999999993</v>
       </c>
     </row>
     <row r="8" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="23">
+      <c r="C8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="10">
         <v>34.97</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="10">
         <v>152.28</v>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="17" t="s">
+      <c r="F8" s="8"/>
+      <c r="G8" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="25">
         <f>D9</f>
         <v>31414.06</v>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="25">
         <f>E9</f>
         <v>20742.57</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="67">
         <f>(I8-J8)/J8</f>
         <v>0.51447289318536715</v>
       </c>
-      <c r="L8" s="14"/>
-      <c r="M8" s="17" t="s">
+      <c r="L8" s="1"/>
+      <c r="M8" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="N8" s="51" t="s">
+      <c r="N8" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="O8" s="39">
+      <c r="O8" s="26">
         <f>I18</f>
         <v>5.8954545845657048E-2</v>
       </c>
-      <c r="P8" s="39">
+      <c r="P8" s="26">
         <f>J18</f>
         <v>8.4937123275097184E-2</v>
       </c>
-      <c r="Q8" s="52" t="s">
+      <c r="Q8" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="R8" s="14"/>
-      <c r="S8" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="T8" s="22" t="s">
+      <c r="R8" s="1"/>
+      <c r="S8" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="T8" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="U8" s="57">
+      <c r="U8" s="44">
         <f>D47</f>
         <v>32701.81</v>
       </c>
-      <c r="V8" s="57">
+      <c r="V8" s="44">
         <f>E47</f>
         <v>8119.8600000000006</v>
       </c>
-      <c r="W8" s="60">
+      <c r="W8" s="47">
         <f>U8-V8</f>
         <v>24581.95</v>
       </c>
     </row>
     <row r="9" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="26">
+      <c r="C9" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="13">
         <f>D8+D7</f>
         <v>31414.06</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="13">
         <f>E8+E7</f>
         <v>20742.57</v>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="34" t="s">
+      <c r="F9" s="8"/>
+      <c r="G9" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="23">
         <f>D21</f>
         <v>1161.48</v>
       </c>
-      <c r="J9" s="36">
+      <c r="J9" s="23">
         <f>E21</f>
         <v>1261.6500000000001</v>
       </c>
-      <c r="K9" s="91">
+      <c r="K9" s="67">
         <f>(I9-J9)/J9</f>
         <v>-7.9396029009630303E-2</v>
       </c>
-      <c r="L9" s="14"/>
-      <c r="M9" s="18" t="s">
+      <c r="L9" s="1"/>
+      <c r="M9" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N9" s="49" t="s">
+      <c r="N9" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="O9" s="47">
+      <c r="O9" s="34">
         <f>I19</f>
         <v>4.935962132745092E-2</v>
       </c>
-      <c r="P9" s="47">
+      <c r="P9" s="34">
         <f>J19</f>
         <v>8.4907011994488815E-2</v>
       </c>
-      <c r="Q9" s="50" t="s">
+      <c r="Q9" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="R9" s="14"/>
-      <c r="S9" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="T9" s="31" t="s">
+      <c r="R9" s="1"/>
+      <c r="S9" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="T9" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="U9" s="61">
+      <c r="U9" s="48">
         <f>U7-U8</f>
         <v>21801.019999999993</v>
       </c>
-      <c r="V9" s="61">
+      <c r="V9" s="48">
         <f>V7-V8</f>
         <v>1710.9699999999993</v>
       </c>
-      <c r="W9" s="62">
+      <c r="W9" s="49">
         <f>U9-V9</f>
         <v>20090.049999999996</v>
       </c>
     </row>
     <row r="10" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="23">
+      <c r="C10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="10">
         <v>24048.83</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="10">
         <v>24851.79</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="17" t="s">
+      <c r="F10" s="8"/>
+      <c r="G10" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I10" s="38">
+      <c r="I10" s="25">
         <f>D16</f>
         <v>29869.64</v>
       </c>
-      <c r="J10" s="38">
+      <c r="J10" s="25">
         <f>E16</f>
         <v>18994.589999999997</v>
       </c>
-      <c r="K10" s="91">
+      <c r="K10" s="67">
         <f>(I10-J10)/J10</f>
         <v>0.57253407417585767</v>
       </c>
-      <c r="L10" s="14"/>
-      <c r="M10" s="17" t="s">
+      <c r="L10" s="1"/>
+      <c r="M10" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="N10" s="51" t="s">
+      <c r="N10" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="O10" s="39">
+      <c r="O10" s="26">
         <f>D21/D41</f>
         <v>5.2876311459811948E-2</v>
       </c>
-      <c r="P10" s="39">
+      <c r="P10" s="26">
         <f>E21/E41</f>
         <v>0.66508695445895305</v>
       </c>
-      <c r="Q10" s="52" t="s">
+      <c r="Q10" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
     </row>
     <row r="11" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="23">
+      <c r="C11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="10">
         <v>5480.32</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="10">
         <v>-6010.38</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="18" t="s">
+      <c r="F11" s="8"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="N11" s="49" t="s">
+      <c r="N11" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="O11" s="47">
+      <c r="O11" s="34">
         <f>D21/D37</f>
         <v>2.12461487834061E-2</v>
       </c>
-      <c r="P11" s="47">
+      <c r="P11" s="34">
         <f>E21/E37</f>
         <v>0.12595314680707051</v>
       </c>
-      <c r="Q11" s="50" t="s">
+      <c r="Q11" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="R11" s="14"/>
-      <c r="S11" s="96" t="s">
-        <v>270</v>
-      </c>
-      <c r="T11" s="19" t="s">
+      <c r="R11" s="1"/>
+      <c r="S11" s="69" t="s">
+        <v>267</v>
+      </c>
+      <c r="T11" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="U11" s="58">
+      <c r="U11" s="45">
         <f>D32</f>
         <v>15138.64</v>
       </c>
-      <c r="V11" s="58">
+      <c r="V11" s="45">
         <f>E32</f>
         <v>267.37</v>
       </c>
-      <c r="W11" s="63">
+      <c r="W11" s="50">
         <f>U11-V11</f>
         <v>14871.269999999999</v>
       </c>
     </row>
     <row r="12" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="23">
+      <c r="C12" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="10">
         <v>39.909999999999997</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="10">
         <v>28.26</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="92"/>
-      <c r="H12" s="92"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="92"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="17" t="s">
+      <c r="F12" s="8"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="85"/>
+      <c r="K12" s="85"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="N12" s="51" t="s">
+      <c r="N12" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="O12" s="39">
+      <c r="O12" s="26">
         <f>(D17+D13)/(D37-D47)</f>
         <v>7.0511764100668506E-2</v>
       </c>
-      <c r="P12" s="39">
+      <c r="P12" s="26">
         <f>(E17+E13)/(E37-E47)</f>
         <v>0.92161142037786981</v>
       </c>
-      <c r="Q12" s="52" t="s">
+      <c r="Q12" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="R12" s="14"/>
-      <c r="S12" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="T12" s="22" t="s">
+      <c r="R12" s="1"/>
+      <c r="S12" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="T12" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="U12" s="57">
+      <c r="U12" s="44">
         <f>D31</f>
         <v>698.71</v>
       </c>
-      <c r="V12" s="57">
+      <c r="V12" s="44">
         <f>E31</f>
         <v>6179.03</v>
       </c>
-      <c r="W12" s="60">
+      <c r="W12" s="47">
         <f>U12-V12</f>
         <v>-5480.32</v>
       </c>
     </row>
     <row r="13" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="23">
+      <c r="C13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="10">
         <v>4.4400000000000004</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="10">
         <v>0.28000000000000003</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="T13" s="19" t="s">
+      <c r="F13" s="8"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="T13" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="U13" s="58">
+      <c r="U13" s="45">
         <f>D33</f>
         <v>97.53</v>
       </c>
-      <c r="V13" s="58">
+      <c r="V13" s="45">
         <f>E33</f>
         <v>785.4</v>
       </c>
-      <c r="W13" s="63">
+      <c r="W13" s="50">
         <f>U13-V13</f>
         <v>-687.87</v>
       </c>
     </row>
     <row r="14" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="23">
+      <c r="C14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="10">
         <v>41.89</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="10">
         <v>3.23</v>
       </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="81" t="s">
-        <v>258</v>
-      </c>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="T14" s="22" t="s">
+      <c r="F14" s="8"/>
+      <c r="G14" s="101" t="s">
+        <v>255</v>
+      </c>
+      <c r="H14" s="101"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="101"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="T14" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="U14" s="57">
+      <c r="U14" s="44">
         <f>D44</f>
         <v>12648.78</v>
       </c>
-      <c r="V14" s="57">
+      <c r="V14" s="44">
         <f>E44</f>
         <v>7577.34</v>
       </c>
-      <c r="W14" s="60">
+      <c r="W14" s="47">
         <f>U14-V14</f>
         <v>5071.4400000000005</v>
       </c>
     </row>
     <row r="15" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="23">
+      <c r="C15" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="10">
         <v>254.25</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="10">
         <v>121.41</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="15" t="s">
+      <c r="F15" s="8"/>
+      <c r="G15" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K15" s="15" t="s">
+      <c r="K15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="14"/>
-      <c r="M15" s="15" t="s">
+      <c r="L15" s="1"/>
+      <c r="M15" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N15" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="O15" s="15" t="s">
+      <c r="N15" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="O15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="P15" s="15" t="s">
+      <c r="P15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q15" s="15" t="s">
+      <c r="Q15" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="R15" s="14"/>
-      <c r="S15" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="T15" s="19" t="s">
+      <c r="R15" s="1"/>
+      <c r="S15" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="T15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="U15" s="58">
+      <c r="U15" s="45">
         <f>D43</f>
         <v>6661.09</v>
       </c>
-      <c r="V15" s="58">
+      <c r="V15" s="45">
         <f>E43</f>
         <v>0</v>
       </c>
-      <c r="W15" s="63">
+      <c r="W15" s="50">
         <f>U15-V15</f>
         <v>6661.09</v>
       </c>
     </row>
     <row r="16" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="26">
+      <c r="C16" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="13">
         <f>SUM(D10:D15)</f>
         <v>29869.64</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="13">
         <f>SUM(E10:E15)</f>
         <v>18994.589999999997</v>
       </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="34" t="s">
+      <c r="F16" s="8"/>
+      <c r="G16" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="I16" s="91">
+      <c r="I16" s="67">
         <f>D21/D7</f>
         <v>3.7014457716906389E-2</v>
       </c>
-      <c r="J16" s="91">
+      <c r="J16" s="67">
         <f>E21/E7</f>
         <v>6.1274027709177482E-2</v>
       </c>
-      <c r="K16" s="37">
+      <c r="K16" s="24">
         <f>I16-J16</f>
         <v>-2.4259569992271093E-2</v>
       </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="34" t="s">
+      <c r="L16" s="1"/>
+      <c r="M16" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="N16" s="49" t="s">
+      <c r="N16" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="O16" s="53">
+      <c r="O16" s="40">
         <f>D36/D47</f>
         <v>1.6666609585218675</v>
       </c>
-      <c r="P16" s="53">
+      <c r="P16" s="40">
         <f>E36/E47</f>
         <v>1.2107142241368694</v>
       </c>
-      <c r="Q16" s="50" t="s">
+      <c r="Q16" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="R16" s="14"/>
-      <c r="S16" s="92"/>
-      <c r="T16" s="92"/>
-      <c r="U16" s="92"/>
-      <c r="V16" s="92"/>
-      <c r="W16" s="92"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="85"/>
+      <c r="T16" s="85"/>
+      <c r="U16" s="85"/>
+      <c r="V16" s="85"/>
+      <c r="W16" s="85"/>
     </row>
     <row r="17" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="29">
+      <c r="C17" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="16">
         <f>D9-D16</f>
         <v>1544.4200000000019</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="16">
         <f>E9-E16</f>
         <v>1747.9800000000032</v>
       </c>
-      <c r="F17" s="21"/>
-      <c r="G17" s="17" t="s">
+      <c r="F17" s="8"/>
+      <c r="G17" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="28">
         <f>D17/D9</f>
         <v>4.916333641687836E-2</v>
       </c>
-      <c r="J17" s="41">
+      <c r="J17" s="28">
         <f>E17/E9</f>
         <v>8.4270174814403576E-2</v>
       </c>
-      <c r="K17" s="39">
+      <c r="K17" s="26">
         <f>I17-J17</f>
         <v>-3.5106838397525215E-2</v>
       </c>
-      <c r="L17" s="14"/>
-      <c r="M17" s="17" t="s">
+      <c r="L17" s="1"/>
+      <c r="M17" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="N17" s="51" t="s">
+      <c r="N17" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="O17" s="54">
-        <f>(D36-D31)/D47</f>
-        <v>1.6452948628837363</v>
-      </c>
-      <c r="P17" s="54">
-        <f>(E36-E31)/E47</f>
-        <v>0.44973681812247995</v>
-      </c>
-      <c r="Q17" s="52" t="s">
+      <c r="O17" s="41">
+        <f>(D33+D32)/D47</f>
+        <v>0.46591213146917554</v>
+      </c>
+      <c r="P17" s="41">
+        <f>(E33+E32)/E47</f>
+        <v>0.1296537132413613</v>
+      </c>
+      <c r="Q17" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="R17" s="14"/>
+      <c r="R17" s="1"/>
     </row>
     <row r="18" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="23">
+      <c r="C18" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="10">
         <v>389.01</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="10">
         <v>484.4</v>
       </c>
-      <c r="F18" s="21"/>
-      <c r="G18" s="34" t="s">
+      <c r="F18" s="8"/>
+      <c r="G18" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="I18" s="40">
+      <c r="I18" s="27">
         <f>(D7-D11-D10)/D7</f>
         <v>5.8954545845657048E-2</v>
       </c>
-      <c r="J18" s="40">
+      <c r="J18" s="27">
         <f>(E7-E11-E10)/E7</f>
         <v>8.4937123275097184E-2</v>
       </c>
-      <c r="K18" s="37">
+      <c r="K18" s="24">
         <f>I18-J18</f>
         <v>-2.5982577429440136E-2</v>
       </c>
-      <c r="L18" s="14"/>
-      <c r="M18" s="18" t="s">
+      <c r="L18" s="1"/>
+      <c r="M18" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="N18" s="49" t="s">
+      <c r="N18" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="O18" s="55">
+      <c r="O18" s="42">
         <f>D33/D47</f>
         <v>2.9824037262769247E-3</v>
       </c>
-      <c r="P18" s="55">
+      <c r="P18" s="42">
         <f>E33/E47</f>
         <v>9.672580561733822E-2</v>
       </c>
-      <c r="Q18" s="50" t="s">
+      <c r="Q18" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="R18" s="14"/>
-      <c r="S18" s="92"/>
-      <c r="T18" s="92"/>
-      <c r="U18" s="92"/>
-      <c r="V18" s="92"/>
-      <c r="W18" s="92"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="85"/>
+      <c r="T18" s="85"/>
+      <c r="U18" s="85"/>
+      <c r="V18" s="85"/>
+      <c r="W18" s="85"/>
     </row>
     <row r="19" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="23">
+      <c r="C19" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="10">
         <v>6.08</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="10">
         <v>-1.92</v>
       </c>
-      <c r="F19" s="21"/>
-      <c r="G19" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="H19" s="22" t="s">
+      <c r="F19" s="8"/>
+      <c r="G19" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="28">
         <f>(D17+D13)/D7</f>
         <v>4.935962132745092E-2</v>
       </c>
-      <c r="J19" s="41">
+      <c r="J19" s="28">
         <f>(E17+E13)/E7</f>
         <v>8.4907011994488815E-2</v>
       </c>
-      <c r="K19" s="39">
+      <c r="K19" s="26">
         <f>I19-J19</f>
         <v>-3.5547390667037895E-2</v>
       </c>
-      <c r="L19" s="14"/>
-      <c r="R19" s="14"/>
+      <c r="L19" s="1"/>
+      <c r="R19" s="1"/>
     </row>
     <row r="20" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="26">
+      <c r="C20" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="13">
         <f>SUM(D18:D19)</f>
         <v>395.09</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="13">
         <f>SUM(E18:E19)</f>
         <v>482.47999999999996</v>
       </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="92"/>
-      <c r="H20" s="92"/>
-      <c r="I20" s="92"/>
-      <c r="J20" s="92"/>
-      <c r="K20" s="92"/>
-      <c r="L20" s="14"/>
-      <c r="R20" s="14"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="1"/>
+      <c r="R20" s="1"/>
     </row>
     <row r="21" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="32">
+      <c r="C21" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="19">
         <v>1161.48</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="19">
         <v>1261.6500000000001</v>
       </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
     </row>
     <row r="22" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="29">
-        <v>0.08</v>
-      </c>
-      <c r="E22" s="29">
-        <v>2.27</v>
-      </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="81" t="s">
-        <v>259</v>
-      </c>
-      <c r="H22" s="81"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="81"/>
-      <c r="K22" s="81"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="81" t="s">
-        <v>265</v>
-      </c>
-      <c r="N22" s="81"/>
-      <c r="O22" s="81"/>
-      <c r="P22" s="81"/>
-      <c r="Q22" s="81"/>
-      <c r="R22" s="14"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="101" t="s">
+        <v>256</v>
+      </c>
+      <c r="H22" s="101"/>
+      <c r="I22" s="101"/>
+      <c r="J22" s="101"/>
+      <c r="K22" s="101"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="101" t="s">
+        <v>262</v>
+      </c>
+      <c r="N22" s="101"/>
+      <c r="O22" s="101"/>
+      <c r="P22" s="101"/>
+      <c r="Q22" s="101"/>
+      <c r="R22" s="1"/>
     </row>
     <row r="23" spans="2:23" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H23" s="15" t="s">
+      <c r="H23" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="15" t="s">
+      <c r="I23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J23" s="15" t="s">
+      <c r="J23" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K23" s="15" t="s">
+      <c r="K23" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L23" s="14"/>
-      <c r="M23" s="15" t="s">
+      <c r="L23" s="1"/>
+      <c r="M23" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N23" s="15" t="s">
+      <c r="N23" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="O23" s="15" t="s">
+      <c r="O23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="P23" s="15" t="s">
+      <c r="P23" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q23" s="15" t="s">
+      <c r="Q23" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="R23" s="14"/>
+      <c r="R23" s="1"/>
     </row>
     <row r="24" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="90" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="G24" s="34" t="s">
+      <c r="C24" s="90"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="90"/>
+      <c r="G24" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I24" s="36">
-        <f>D10</f>
+      <c r="I24" s="23">
+        <f t="shared" ref="I24:J29" si="0">D10</f>
         <v>24048.83</v>
       </c>
-      <c r="J24" s="36">
-        <f>E10</f>
+      <c r="J24" s="23">
+        <f t="shared" si="0"/>
         <v>24851.79</v>
       </c>
-      <c r="K24" s="40">
+      <c r="K24" s="27">
         <f>(I24-J24)/J24</f>
         <v>-3.2309946285559277E-2</v>
       </c>
-      <c r="L24" s="14"/>
-      <c r="M24" s="34" t="s">
+      <c r="L24" s="1"/>
+      <c r="M24" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="N24" s="49" t="s">
+      <c r="N24" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="O24" s="53">
+      <c r="O24" s="40">
         <f>D43/D41</f>
         <v>0.30324574637689738</v>
       </c>
-      <c r="P24" s="53">
+      <c r="P24" s="40">
         <f>E43/E41</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="50" t="s">
+      <c r="Q24" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="R24" s="14"/>
+      <c r="R24" s="1"/>
     </row>
     <row r="25" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G25" s="17" t="s">
+      <c r="G25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I25" s="38">
-        <f>D11</f>
+      <c r="I25" s="25">
+        <f t="shared" si="0"/>
         <v>5480.32</v>
       </c>
-      <c r="J25" s="38">
-        <f>E11</f>
+      <c r="J25" s="25">
+        <f t="shared" si="0"/>
         <v>-6010.38</v>
       </c>
-      <c r="K25" s="41">
+      <c r="K25" s="28">
         <f>(I25+J25)/J25</f>
         <v>8.8190763312802248E-2</v>
       </c>
-      <c r="L25" s="14"/>
-      <c r="M25" s="17" t="s">
+      <c r="L25" s="1"/>
+      <c r="M25" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="N25" s="51" t="s">
+      <c r="N25" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="O25" s="54">
+      <c r="O25" s="41">
         <f>D43/D37</f>
         <v>0.12184670351590948</v>
       </c>
-      <c r="P25" s="54">
+      <c r="P25" s="41">
         <f>E43/E37</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="52" t="s">
+      <c r="Q25" s="39" t="s">
         <v>151</v>
       </c>
-      <c r="R25" s="14"/>
+      <c r="R25" s="1"/>
     </row>
     <row r="26" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="81" t="s">
+      <c r="B26" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="81"/>
-      <c r="D26" s="81"/>
-      <c r="E26" s="81"/>
-      <c r="G26" s="18" t="s">
+      <c r="C26" s="101"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="101"/>
+      <c r="G26" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H26" s="19" t="s">
+      <c r="H26" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I26" s="42">
-        <f>D12</f>
+      <c r="I26" s="29">
+        <f t="shared" si="0"/>
         <v>39.909999999999997</v>
       </c>
-      <c r="J26" s="42">
-        <f>E12</f>
+      <c r="J26" s="29">
+        <f t="shared" si="0"/>
         <v>28.26</v>
       </c>
-      <c r="K26" s="41">
+      <c r="K26" s="28">
         <f>(I26-J26)/J26</f>
         <v>0.41224345364472731</v>
       </c>
-      <c r="L26" s="14"/>
-      <c r="M26" s="18" t="s">
+      <c r="L26" s="1"/>
+      <c r="M26" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="N26" s="49" t="s">
+      <c r="N26" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="O26" s="55">
+      <c r="O26" s="42">
         <f>(D17+D13)/D13</f>
         <v>348.84234234234276</v>
       </c>
-      <c r="P26" s="55">
+      <c r="P26" s="42">
         <f>(E17+E13)/E13</f>
         <v>6243.7857142857247</v>
       </c>
-      <c r="Q26" s="50" t="s">
+      <c r="Q26" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="R26" s="14"/>
+      <c r="R26" s="1"/>
     </row>
     <row r="27" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="23">
+      <c r="C27" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="10">
         <v>91.63</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="10">
         <v>118.74</v>
       </c>
-      <c r="F27" s="21"/>
-      <c r="G27" s="17" t="s">
+      <c r="F27" s="8"/>
+      <c r="G27" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="H27" s="22" t="s">
+      <c r="H27" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I27" s="38">
-        <f>D13</f>
+      <c r="I27" s="25">
+        <f t="shared" si="0"/>
         <v>4.4400000000000004</v>
       </c>
-      <c r="J27" s="38">
-        <f>E13</f>
+      <c r="J27" s="25">
+        <f t="shared" si="0"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="K27" s="41">
+      <c r="K27" s="28">
         <f>(I27-J27)/J27</f>
         <v>14.857142857142856</v>
       </c>
-      <c r="L27" s="14"/>
-      <c r="M27" s="17" t="s">
+      <c r="L27" s="1"/>
+      <c r="M27" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="N27" s="51" t="s">
+      <c r="N27" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="O27" s="54">
+      <c r="O27" s="41">
         <f>D37/D41</f>
         <v>2.4887480549467855</v>
       </c>
-      <c r="P27" s="54">
+      <c r="P27" s="41">
         <f>E37/E41</f>
         <v>5.2804314248512094</v>
       </c>
-      <c r="Q27" s="52" t="s">
+      <c r="Q27" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="R27" s="14"/>
+      <c r="R27" s="1"/>
     </row>
     <row r="28" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="23">
+      <c r="C28" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="10">
         <v>67.25</v>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="10">
         <v>67.25</v>
       </c>
-      <c r="F28" s="21"/>
-      <c r="G28" s="18" t="s">
+      <c r="F28" s="8"/>
+      <c r="G28" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H28" s="19" t="s">
+      <c r="H28" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I28" s="42">
-        <f>D14</f>
+      <c r="I28" s="29">
+        <f t="shared" si="0"/>
         <v>41.89</v>
       </c>
-      <c r="J28" s="42">
-        <f>E14</f>
+      <c r="J28" s="29">
+        <f t="shared" si="0"/>
         <v>3.23</v>
       </c>
-      <c r="K28" s="41">
+      <c r="K28" s="28">
         <f>(I28-J28)/J28</f>
         <v>11.96904024767802</v>
       </c>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="14"/>
-      <c r="R28" s="14"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
     </row>
     <row r="29" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="23">
+      <c r="C29" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="10">
         <v>6.08</v>
       </c>
-      <c r="E29" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="F29" s="21"/>
-      <c r="G29" s="17" t="s">
+      <c r="E29" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H29" s="22" t="s">
+      <c r="H29" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I29" s="38">
-        <f>D15</f>
+      <c r="I29" s="25">
+        <f t="shared" si="0"/>
         <v>254.25</v>
       </c>
-      <c r="J29" s="38">
-        <f>E15</f>
+      <c r="J29" s="25">
+        <f t="shared" si="0"/>
         <v>121.41</v>
       </c>
-      <c r="K29" s="41">
+      <c r="K29" s="28">
         <f>(I29-J29)/J29</f>
         <v>1.0941438102298</v>
       </c>
-      <c r="L29" s="14"/>
-      <c r="M29" s="81" t="s">
-        <v>266</v>
-      </c>
-      <c r="N29" s="81"/>
-      <c r="O29" s="81"/>
-      <c r="P29" s="81"/>
-      <c r="Q29" s="81"/>
-      <c r="R29" s="14"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="101" t="s">
+        <v>263</v>
+      </c>
+      <c r="N29" s="101"/>
+      <c r="O29" s="101"/>
+      <c r="P29" s="101"/>
+      <c r="Q29" s="101"/>
+      <c r="R29" s="1"/>
     </row>
     <row r="30" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="26">
+      <c r="C30" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="13">
         <f>SUM(D27:D29)</f>
         <v>164.96</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="13">
         <f>SUM(E27:E29)</f>
         <v>185.99</v>
       </c>
-      <c r="F30" s="21"/>
-      <c r="G30" s="24" t="s">
+      <c r="F30" s="8"/>
+      <c r="G30" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H30" s="25" t="s">
+      <c r="H30" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="31">
         <f>SUM(I24:I29)</f>
         <v>29869.64</v>
       </c>
-      <c r="J30" s="44">
+      <c r="J30" s="31">
         <f>SUM(J24:J29)</f>
         <v>18994.589999999997</v>
       </c>
-      <c r="K30" s="41">
+      <c r="K30" s="28">
         <f>(I30-J30)/J30</f>
         <v>0.57253407417585767</v>
       </c>
-      <c r="L30" s="14"/>
-      <c r="M30" s="15" t="s">
+      <c r="L30" s="1"/>
+      <c r="M30" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N30" s="15" t="s">
+      <c r="N30" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="O30" s="15" t="s">
+      <c r="O30" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="P30" s="15" t="s">
+      <c r="P30" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q30" s="15" t="s">
+      <c r="Q30" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="R30" s="14"/>
+      <c r="R30" s="1"/>
     </row>
     <row r="31" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" s="23">
+      <c r="C31" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="10">
         <v>698.71</v>
       </c>
-      <c r="E31" s="23">
+      <c r="E31" s="10">
         <v>6179.03</v>
       </c>
-      <c r="F31" s="21"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="34" t="s">
+      <c r="F31" s="8"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="N31" s="49" t="s">
+      <c r="N31" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="O31" s="53">
+      <c r="O31" s="40">
         <f>D7/D37</f>
         <v>0.57399594898568251</v>
       </c>
-      <c r="P31" s="53">
+      <c r="P31" s="40">
         <f>E7/E37</f>
         <v>2.0555715286887457</v>
       </c>
-      <c r="Q31" s="50" t="s">
+      <c r="Q31" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="R31" s="14"/>
+      <c r="R31" s="1"/>
     </row>
     <row r="32" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="23">
+      <c r="C32" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="10">
         <v>15138.64</v>
       </c>
-      <c r="E32" s="23">
+      <c r="E32" s="10">
         <v>267.37</v>
       </c>
-      <c r="F32" s="21"/>
-      <c r="G32" s="82" t="s">
-        <v>255</v>
-      </c>
-      <c r="H32" s="82"/>
-      <c r="I32" s="82"/>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="17" t="s">
+      <c r="F32" s="8"/>
+      <c r="G32" s="104" t="s">
+        <v>252</v>
+      </c>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="N32" s="51" t="s">
+      <c r="N32" s="38" t="s">
         <v>162</v>
       </c>
-      <c r="O32" s="54">
+      <c r="O32" s="41">
         <f>D10/((E31+D31)/2)</f>
         <v>6.9932361502470295</v>
       </c>
-      <c r="P32" s="54">
+      <c r="P32" s="41">
         <f>E10/((F31+E31)/2)</f>
         <v>8.0439130413673343</v>
       </c>
-      <c r="Q32" s="52" t="s">
+      <c r="Q32" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="R32" s="14"/>
+      <c r="R32" s="1"/>
     </row>
     <row r="33" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="23">
+      <c r="C33" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="10">
         <v>97.53</v>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="10">
         <v>785.4</v>
       </c>
-      <c r="F33" s="21"/>
-      <c r="G33" s="46" t="s">
+      <c r="F33" s="8"/>
+      <c r="G33" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="H33" s="46" t="s">
+      <c r="H33" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="I33" s="46" t="s">
+      <c r="I33" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="J33" s="46" t="s">
+      <c r="J33" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="K33" s="46" t="s">
+      <c r="K33" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="L33" s="14"/>
-      <c r="M33" s="18" t="s">
+      <c r="L33" s="1"/>
+      <c r="M33" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="N33" s="49" t="s">
+      <c r="N33" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="O33" s="55">
+      <c r="O33" s="42">
         <f>D7/((E32+D32)/2)</f>
         <v>4.0736167249015161</v>
       </c>
-      <c r="P33" s="55">
+      <c r="P33" s="42">
         <f>E7/((F32+E32)/2)</f>
         <v>154.02094475820024</v>
       </c>
-      <c r="Q33" s="50" t="s">
+      <c r="Q33" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="R33" s="14"/>
+      <c r="R33" s="1"/>
     </row>
     <row r="34" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" s="23">
+      <c r="C34" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="10">
         <v>38521.11</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="10">
         <v>2463.2800000000002</v>
       </c>
-      <c r="F34" s="21"/>
-      <c r="G34" s="18" t="s">
+      <c r="F34" s="8"/>
+      <c r="G34" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="H34" s="19" t="s">
+      <c r="H34" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="30">
         <f>D10/D7</f>
         <v>0.76639666733483991</v>
       </c>
-      <c r="J34" s="43">
+      <c r="J34" s="30">
         <f>E10/E7</f>
         <v>1.2069664876016801</v>
       </c>
-      <c r="K34" s="47">
+      <c r="K34" s="34">
         <f>I34-J34</f>
         <v>-0.44056982026684022</v>
       </c>
-      <c r="L34" s="14"/>
-      <c r="M34" s="17" t="s">
+      <c r="L34" s="1"/>
+      <c r="M34" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="N34" s="51" t="s">
+      <c r="N34" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="O34" s="54">
+      <c r="O34" s="41">
         <f>365/O33</f>
         <v>89.600967555145786</v>
       </c>
-      <c r="P34" s="54">
+      <c r="P34" s="41">
         <f>365/P33</f>
         <v>2.369807564633621</v>
       </c>
-      <c r="Q34" s="52" t="s">
+      <c r="Q34" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="R34" s="14"/>
+      <c r="R34" s="1"/>
     </row>
     <row r="35" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="23">
+      <c r="C35" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="10">
         <v>46.84</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="10">
         <v>135.75</v>
       </c>
-      <c r="F35" s="21"/>
-      <c r="G35" s="17" t="s">
+      <c r="F35" s="8"/>
+      <c r="G35" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="I35" s="41">
+      <c r="I35" s="28">
         <f>D12/D7</f>
         <v>1.2718660738727603E-3</v>
       </c>
-      <c r="J35" s="41">
+      <c r="J35" s="28">
         <f>E12/E7</f>
         <v>1.372491596767214E-3</v>
       </c>
-      <c r="K35" s="39">
+      <c r="K35" s="26">
         <f>I35-J35</f>
         <v>-1.0062552289445367E-4</v>
       </c>
-      <c r="L35" s="14"/>
-      <c r="M35" s="18" t="s">
+      <c r="L35" s="1"/>
+      <c r="M35" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="N35" s="49" t="s">
+      <c r="N35" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="O35" s="55">
+      <c r="O35" s="42">
         <f>D10/((E44+D44)/2)</f>
         <v>2.3779973618271817</v>
       </c>
-      <c r="P35" s="55">
+      <c r="P35" s="42">
         <f>E10/((F44+E44)/2)</f>
         <v>6.5595024111363616</v>
       </c>
-      <c r="Q35" s="50" t="s">
+      <c r="Q35" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="R35" s="14"/>
+      <c r="R35" s="1"/>
     </row>
     <row r="36" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="26">
+      <c r="C36" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="13">
         <f>SUM(D31:D35)</f>
         <v>54502.829999999994</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="13">
         <f>SUM(E31:E35)</f>
         <v>9830.83</v>
       </c>
-      <c r="F36" s="21"/>
-      <c r="G36" s="18" t="s">
+      <c r="F36" s="8"/>
+      <c r="G36" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H36" s="19" t="s">
+      <c r="H36" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="I36" s="43">
+      <c r="I36" s="30">
         <f>D15/D7</f>
         <v>8.1025294232560593E-3</v>
       </c>
-      <c r="J36" s="43">
+      <c r="J36" s="30">
         <f>E15/E7</f>
         <v>5.8964686752833494E-3</v>
       </c>
-      <c r="K36" s="47">
+      <c r="K36" s="34">
         <f>I36-J36</f>
         <v>2.2060607479727099E-3</v>
       </c>
-      <c r="L36" s="14"/>
-      <c r="M36" s="17" t="s">
+      <c r="L36" s="1"/>
+      <c r="M36" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="N36" s="51" t="s">
+      <c r="N36" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="O36" s="54">
+      <c r="O36" s="41">
         <f>365/O35</f>
         <v>153.49049829035343</v>
       </c>
-      <c r="P36" s="54">
+      <c r="P36" s="41">
         <f>365/P35</f>
         <v>55.64446464419666</v>
       </c>
-      <c r="Q36" s="52" t="s">
+      <c r="Q36" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="R36" s="14"/>
+      <c r="R36" s="1"/>
     </row>
     <row r="37" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="30" t="s">
+      <c r="B37" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="32">
+      <c r="C37" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="19">
         <f>D36+D30</f>
         <v>54667.789999999994</v>
       </c>
-      <c r="E37" s="32">
+      <c r="E37" s="19">
         <f>E36+E30</f>
         <v>10016.82</v>
       </c>
-      <c r="F37" s="21"/>
-      <c r="G37" s="24" t="s">
+      <c r="F37" s="8"/>
+      <c r="G37" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="H37" s="25" t="s">
+      <c r="H37" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I37" s="45">
+      <c r="I37" s="32">
         <f>D16/D7</f>
         <v>0.95189631056859836</v>
       </c>
-      <c r="J37" s="45">
+      <c r="J37" s="32">
         <f>E16/E7</f>
         <v>0.92250230569846248</v>
       </c>
-      <c r="K37" s="48">
+      <c r="K37" s="35">
         <f>I37-J37</f>
         <v>2.9394004870135881E-2</v>
       </c>
-      <c r="L37" s="14"/>
-      <c r="M37" s="18" t="s">
+      <c r="L37" s="1"/>
+      <c r="M37" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="N37" s="49" t="s">
+      <c r="N37" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="O37" s="55">
+      <c r="O37" s="42">
         <f>D7/(D36-D47)</f>
         <v>1.4393404528778933</v>
       </c>
-      <c r="P37" s="55">
+      <c r="P37" s="42">
         <f>E7/(E36-E47)</f>
         <v>12.034278800914107</v>
       </c>
-      <c r="Q37" s="50" t="s">
+      <c r="Q37" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="R37" s="14"/>
+      <c r="R37" s="1"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="81" t="s">
+      <c r="B38" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="81"/>
-      <c r="D38" s="81"/>
-      <c r="E38" s="81"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14"/>
-      <c r="P38" s="14"/>
-      <c r="Q38" s="14"/>
-      <c r="R38" s="14"/>
+      <c r="C38" s="101"/>
+      <c r="D38" s="101"/>
+      <c r="E38" s="101"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
     </row>
     <row r="39" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C39" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D39" s="23">
+      <c r="C39" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="10">
         <v>13923.94</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="10">
         <v>555.54</v>
       </c>
-      <c r="F39" s="21"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="95" t="s">
-        <v>269</v>
-      </c>
-      <c r="N39" s="81"/>
-      <c r="O39" s="81"/>
-      <c r="P39" s="81"/>
-      <c r="Q39" s="81"/>
-      <c r="R39" s="14"/>
+      <c r="F39" s="8"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="89" t="s">
+        <v>266</v>
+      </c>
+      <c r="N39" s="101"/>
+      <c r="O39" s="101"/>
+      <c r="P39" s="101"/>
+      <c r="Q39" s="101"/>
+      <c r="R39" s="1"/>
     </row>
     <row r="40" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C40" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="23">
+      <c r="C40" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="10">
         <v>8042.04</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="10">
         <v>1341.43</v>
       </c>
-      <c r="F40" s="21"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="15" t="s">
+      <c r="F40" s="8"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N40" s="15" t="s">
+      <c r="N40" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="O40" s="15" t="s">
+      <c r="O40" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="P40" s="15" t="s">
+      <c r="P40" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q40" s="15" t="s">
+      <c r="Q40" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="R40" s="14"/>
+      <c r="R40" s="1"/>
     </row>
     <row r="41" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C41" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="26">
+      <c r="C41" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" s="13">
         <f>SUM(D39:D40)</f>
         <v>21965.98</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="13">
         <f>SUM(E39:E40)</f>
         <v>1896.97</v>
       </c>
-      <c r="F41" s="21"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="34" t="s">
+      <c r="F41" s="8"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="N41" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="N41" s="49" t="s">
+      <c r="O41" s="43">
+        <f>D21/D80</f>
+        <v>8.3416044596572522E-2</v>
+      </c>
+      <c r="P41" s="43">
+        <f>E21/E80</f>
+        <v>2.2710335889404907</v>
+      </c>
+      <c r="Q41" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="O41" s="56">
-        <f>IF(Analysis!D80&lt;&gt;0,Analysis!D21*100000/Analysis!D80/100000,0)</f>
-        <v>0.79804864642022799</v>
-      </c>
-      <c r="P41" s="56">
-        <f>IF(Analysis!E80&lt;&gt;0,Analysis!E21*100000/Analysis!E80/100000,0)</f>
-        <v>2.2710335889404907</v>
-      </c>
-      <c r="Q41" s="50" t="s">
+      <c r="R41" s="1"/>
+    </row>
+    <row r="42" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" s="10">
+        <v>0</v>
+      </c>
+      <c r="E42" s="10">
+        <v>1.92</v>
+      </c>
+      <c r="F42" s="8"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="R41" s="14"/>
-    </row>
-    <row r="42" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D42" s="23">
+      <c r="N42" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="O42" s="44">
+        <f>D41/D79</f>
+        <v>15.775692799595516</v>
+      </c>
+      <c r="P42" s="44">
+        <f>E41/E79</f>
+        <v>34.146416099650793</v>
+      </c>
+      <c r="Q42" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="R42" s="1"/>
+    </row>
+    <row r="43" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D43" s="10">
+        <v>6661.09</v>
+      </c>
+      <c r="E43" s="10">
         <v>0</v>
       </c>
-      <c r="E42" s="23">
-        <v>1.92</v>
-      </c>
-      <c r="F42" s="21"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="N42" s="51" t="s">
+      <c r="F43" s="8"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="O42" s="57">
-        <f>IF(Analysis!D79&lt;&gt;0,Analysis!D33*100/Analysis!D79,0)</f>
-        <v>0.70044829265279795</v>
-      </c>
-      <c r="P42" s="57">
-        <f>IF(Analysis!E79&lt;&gt;0,Analysis!E33*100/Analysis!E79,0)</f>
-        <v>141.37595852683876</v>
-      </c>
-      <c r="Q42" s="52" t="s">
+      <c r="N43" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="R42" s="14"/>
-    </row>
-    <row r="43" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" s="23">
-        <v>6661.09</v>
-      </c>
-      <c r="E43" s="23">
-        <v>0</v>
-      </c>
-      <c r="F43" s="21"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="18" t="s">
+      <c r="O43" s="45">
+        <f>D62/D79</f>
+        <v>-18.843279991151931</v>
+      </c>
+      <c r="P43" s="45">
+        <f>E62/E79</f>
+        <v>19.127335565395832</v>
+      </c>
+      <c r="Q43" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="N43" s="49" t="s">
+      <c r="R43" s="1"/>
+    </row>
+    <row r="44" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D44" s="10">
+        <v>12648.78</v>
+      </c>
+      <c r="E44" s="10">
+        <v>7577.34</v>
+      </c>
+      <c r="F44" s="8"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="O43" s="58">
-        <f>IF(Analysis!D79&lt;&gt;0,Analysis!D62*100/Analysis!D79,0)</f>
-        <v>-188.43279991151928</v>
-      </c>
-      <c r="P43" s="58">
-        <f>IF(Analysis!E79&lt;&gt;0,Analysis!E62*100/Analysis!E79,0)</f>
-        <v>191.2733556539583</v>
-      </c>
-      <c r="Q43" s="50" t="s">
+      <c r="N44" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="R43" s="14"/>
-    </row>
-    <row r="44" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D44" s="23">
-        <v>12648.78</v>
-      </c>
-      <c r="E44" s="23">
-        <v>7577.34</v>
-      </c>
-      <c r="F44" s="21"/>
-      <c r="L44" s="14"/>
-      <c r="M44" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="N44" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="O44" s="57">
+      <c r="O44" s="44">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="P44" s="57">
+      <c r="P44" s="44">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="Q44" s="52" t="s">
-        <v>190</v>
-      </c>
-      <c r="R44" s="14"/>
+      <c r="Q44" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="R44" s="1"/>
     </row>
     <row r="45" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C45" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D45" s="23">
+      <c r="C45" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" s="10">
         <v>389.39</v>
       </c>
-      <c r="E45" s="23">
+      <c r="E45" s="10">
         <v>488.35</v>
       </c>
-      <c r="F45" s="21"/>
-      <c r="L45" s="14"/>
-      <c r="M45" s="14"/>
-      <c r="N45" s="14"/>
-      <c r="O45" s="14"/>
-      <c r="P45" s="14"/>
-      <c r="Q45" s="14"/>
-      <c r="R45" s="14"/>
+      <c r="F45" s="8"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
     </row>
     <row r="46" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C46" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D46" s="23">
+      <c r="C46" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D46" s="10">
         <v>13002.55</v>
       </c>
-      <c r="E46" s="23">
+      <c r="E46" s="10">
         <v>52.25</v>
       </c>
-      <c r="F46" s="21"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="95" t="s">
-        <v>268</v>
-      </c>
-      <c r="N46" s="81"/>
-      <c r="O46" s="81"/>
-      <c r="P46" s="81"/>
-      <c r="Q46" s="81"/>
-      <c r="R46" s="14"/>
+      <c r="F46" s="8"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="89" t="s">
+        <v>265</v>
+      </c>
+      <c r="N46" s="101"/>
+      <c r="O46" s="101"/>
+      <c r="P46" s="101"/>
+      <c r="Q46" s="101"/>
+      <c r="R46" s="1"/>
     </row>
     <row r="47" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="24" t="s">
+      <c r="B47" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C47" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D47" s="26">
+      <c r="C47" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" s="13">
         <f>SUM(D42:D46)</f>
         <v>32701.81</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="13">
         <f>SUM(E42:E46)</f>
         <v>8119.8600000000006</v>
       </c>
-      <c r="F47" s="21"/>
-      <c r="L47" s="14"/>
-      <c r="M47" s="15" t="s">
+      <c r="F47" s="8"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N47" s="15" t="s">
+      <c r="N47" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="O47" s="15" t="s">
+      <c r="O47" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="P47" s="15" t="s">
+      <c r="P47" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q47" s="15" t="s">
+      <c r="Q47" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="R47" s="14"/>
+      <c r="R47" s="1"/>
     </row>
     <row r="48" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="30" t="s">
+      <c r="B48" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C48" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D48" s="32">
+      <c r="C48" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" s="19">
         <f>D47+D41</f>
         <v>54667.79</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="19">
         <f>E47+E41</f>
         <v>10016.83</v>
       </c>
-      <c r="F48" s="21"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="N48" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="O48" s="53">
+      <c r="F48" s="8"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="N48" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="O48" s="40">
         <f>D62/D21</f>
         <v>-22.589515101422322</v>
       </c>
-      <c r="P48" s="53">
+      <c r="P48" s="40">
         <f>E62/E21</f>
         <v>0.84223041255498743</v>
       </c>
-      <c r="Q48" s="50" t="s">
+      <c r="Q48" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="R48" s="1"/>
+    </row>
+    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="L49" s="1"/>
+      <c r="M49" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="N49" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="R48" s="14"/>
-    </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="L49" s="14"/>
-      <c r="M49" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="N49" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="O49" s="39">
+      <c r="O49" s="26">
         <f>D62/D7</f>
         <v>-0.83613865156701483</v>
       </c>
-      <c r="P49" s="39">
+      <c r="P49" s="26">
         <f>E62/E7</f>
         <v>5.1606849636406278E-2</v>
       </c>
-      <c r="Q49" s="52" t="s">
+      <c r="Q49" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="R49" s="1"/>
+    </row>
+    <row r="50" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="90" t="s">
+        <v>78</v>
+      </c>
+      <c r="C50" s="90"/>
+      <c r="D50" s="90"/>
+      <c r="E50" s="90"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="N50" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="R49" s="14"/>
-    </row>
-    <row r="50" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="N50" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="O50" s="47">
+      <c r="O50" s="34">
         <f>D62/D37</f>
         <v>-0.47994019878981764</v>
       </c>
-      <c r="P50" s="47">
+      <c r="P50" s="34">
         <f>E62/E37</f>
         <v>0.1060815707979179</v>
       </c>
-      <c r="Q50" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="R50" s="14"/>
+      <c r="Q50" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="R50" s="1"/>
     </row>
     <row r="51" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D51" s="15" t="s">
+      <c r="D51" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="52" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C52" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D52" s="35">
+      <c r="C52" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" s="22">
         <v>1544.41</v>
       </c>
-      <c r="E52" s="35">
+      <c r="E52" s="22">
         <v>1747.98</v>
       </c>
-      <c r="F52" s="21"/>
+      <c r="F52" s="8"/>
     </row>
     <row r="53" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C53" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D53" s="23">
+      <c r="C53" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D53" s="10">
         <v>41.89</v>
       </c>
-      <c r="E53" s="23">
+      <c r="E53" s="10">
         <v>3.23</v>
       </c>
-      <c r="F53" s="21"/>
+      <c r="F53" s="8"/>
     </row>
     <row r="54" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="17" t="s">
+      <c r="B54" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D54" s="23">
+      <c r="C54" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D54" s="10">
         <v>4.4400000000000004</v>
       </c>
-      <c r="E54" s="23">
+      <c r="E54" s="10">
         <v>0.28000000000000003</v>
       </c>
-      <c r="F54" s="21"/>
+      <c r="F54" s="8"/>
     </row>
     <row r="55" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C55" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="D55" s="26">
+      <c r="C55" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D55" s="13">
         <f>D52+D53+D54</f>
         <v>1590.7400000000002</v>
       </c>
-      <c r="E55" s="26">
+      <c r="E55" s="13">
         <f>E52+E53+E54</f>
         <v>1751.49</v>
       </c>
-      <c r="F55" s="21"/>
+      <c r="F55" s="8"/>
     </row>
     <row r="56" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D56" s="23">
+      <c r="C56" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D56" s="10">
         <v>12851.33</v>
       </c>
-      <c r="E56" s="23">
+      <c r="E56" s="10">
         <v>52.25</v>
       </c>
-      <c r="F56" s="21"/>
+      <c r="F56" s="8"/>
     </row>
     <row r="57" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="17" t="s">
+      <c r="B57" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D57" s="23">
+      <c r="C57" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D57" s="10">
         <v>5480.32</v>
       </c>
-      <c r="E57" s="23">
+      <c r="E57" s="10">
         <v>-6010.38</v>
       </c>
-      <c r="F57" s="21"/>
+      <c r="F57" s="8"/>
     </row>
     <row r="58" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="17" t="s">
+      <c r="B58" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C58" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D58" s="23">
+      <c r="C58" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D58" s="10">
         <v>5071.45</v>
       </c>
-      <c r="E58" s="23">
+      <c r="E58" s="10">
         <v>7577.34</v>
       </c>
-      <c r="F58" s="21"/>
+      <c r="F58" s="8"/>
     </row>
     <row r="59" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C59" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D59" s="23">
+      <c r="C59" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D59" s="10">
         <v>-14871.27</v>
       </c>
-      <c r="E59" s="23">
+      <c r="E59" s="10">
         <v>-41.07</v>
       </c>
-      <c r="F59" s="21"/>
+      <c r="F59" s="8"/>
     </row>
     <row r="60" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="17" t="s">
+      <c r="B60" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C60" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D60" s="23">
+      <c r="C60" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" s="10">
         <v>-35968.910000000003</v>
       </c>
-      <c r="E60" s="23">
+      <c r="E60" s="10">
         <v>-2239.2399999999998</v>
       </c>
-      <c r="F60" s="21"/>
+      <c r="F60" s="8"/>
     </row>
     <row r="61" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="C61" s="22" t="str">
+      <c r="B61" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C61" s="9" t="str">
         <f>C60</f>
         <v>₹</v>
       </c>
-      <c r="D61" s="23">
+      <c r="D61" s="10">
         <v>390.94</v>
       </c>
-      <c r="E61" s="23">
+      <c r="E61" s="10">
         <v>27.79</v>
       </c>
-      <c r="F61" s="21"/>
+      <c r="F61" s="8"/>
     </row>
     <row r="62" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="27" t="s">
+      <c r="B62" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C62" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D62" s="29">
+      <c r="C62" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D62" s="16">
         <v>-26237.27</v>
       </c>
-      <c r="E62" s="29">
+      <c r="E62" s="16">
         <v>1062.5999999999999</v>
       </c>
-      <c r="F62" s="21"/>
+      <c r="F62" s="8"/>
     </row>
     <row r="63" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="17" t="s">
+      <c r="B63" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C63" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D63" s="23">
+      <c r="C63" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D63" s="10">
         <v>-14.78</v>
       </c>
-      <c r="E63" s="23">
+      <c r="E63" s="10">
         <v>-121.98</v>
       </c>
-      <c r="F63" s="21"/>
+      <c r="F63" s="8"/>
     </row>
     <row r="64" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="17" t="s">
+      <c r="B64" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C64" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D64" s="23">
+      <c r="C64" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D64" s="10">
         <v>0</v>
       </c>
-      <c r="E64" s="23">
+      <c r="E64" s="10">
         <v>-67.25</v>
       </c>
-      <c r="F64" s="21"/>
+      <c r="F64" s="8"/>
     </row>
     <row r="65" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="27" t="s">
+      <c r="B65" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C65" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D65" s="29">
+      <c r="C65" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D65" s="16">
         <v>-14.78</v>
       </c>
-      <c r="E65" s="29">
+      <c r="E65" s="16">
         <v>-189.23</v>
       </c>
-      <c r="F65" s="21"/>
+      <c r="F65" s="8"/>
     </row>
     <row r="66" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C66" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D66" s="23">
+      <c r="C66" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D66" s="10">
         <v>19463.060000000001</v>
       </c>
-      <c r="E66" s="23">
+      <c r="E66" s="10">
         <v>0</v>
       </c>
-      <c r="F66" s="21"/>
+      <c r="F66" s="8"/>
     </row>
     <row r="67" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="17" t="s">
+      <c r="B67" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C67" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D67" s="23">
+      <c r="C67" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D67" s="10">
         <v>6661.09</v>
       </c>
-      <c r="E67" s="23">
+      <c r="E67" s="10">
         <v>-94.49</v>
       </c>
-      <c r="F67" s="21"/>
+      <c r="F67" s="8"/>
     </row>
     <row r="68" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="C68" s="22" t="str">
+      <c r="B68" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C68" s="9" t="str">
         <f>C67</f>
         <v>₹</v>
       </c>
-      <c r="D68" s="23">
+      <c r="D68" s="10">
         <v>-555.54</v>
       </c>
-      <c r="E68" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="F68" s="21"/>
+      <c r="E68" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F68" s="8"/>
     </row>
     <row r="69" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="17" t="s">
+      <c r="B69" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C69" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D69" s="23">
+      <c r="C69" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D69" s="10">
         <v>-4.4400000000000004</v>
       </c>
-      <c r="E69" s="23">
+      <c r="E69" s="10">
         <v>-0.28000000000000003</v>
       </c>
-      <c r="F69" s="21"/>
+      <c r="F69" s="8"/>
     </row>
     <row r="70" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C70" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D70" s="29">
+      <c r="C70" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D70" s="16">
         <v>25564.18</v>
       </c>
-      <c r="E70" s="29">
+      <c r="E70" s="16">
         <v>-94.77</v>
       </c>
-      <c r="F70" s="21"/>
+      <c r="F70" s="8"/>
     </row>
     <row r="71" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="30" t="s">
+      <c r="B71" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C71" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D71" s="32">
+      <c r="C71" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D71" s="19">
         <f>D62+D65+D70</f>
         <v>-687.86999999999898</v>
       </c>
-      <c r="E71" s="32">
+      <c r="E71" s="19">
         <f>E62+E65+E70</f>
         <v>778.59999999999991</v>
       </c>
-      <c r="F71" s="21"/>
+      <c r="F71" s="8"/>
     </row>
     <row r="72" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="17" t="s">
+      <c r="B72" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C72" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D72" s="23">
+      <c r="C72" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D72" s="10">
         <v>785.41</v>
       </c>
-      <c r="E72" s="23">
+      <c r="E72" s="10">
         <v>6.8</v>
       </c>
-      <c r="F72" s="21"/>
+      <c r="F72" s="8"/>
     </row>
     <row r="73" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="30" t="s">
+      <c r="B73" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C73" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D73" s="32">
+      <c r="C73" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D73" s="19">
         <v>97.53</v>
       </c>
-      <c r="E73" s="32">
+      <c r="E73" s="19">
         <v>785.41</v>
       </c>
-      <c r="F73" s="21"/>
+      <c r="F73" s="8"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="5" t="s">
+      <c r="B75" s="90" t="s">
         <v>98</v>
       </c>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
+      <c r="C75" s="90"/>
+      <c r="D75" s="90"/>
+      <c r="E75" s="90"/>
     </row>
     <row r="76" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="15" t="s">
+      <c r="B76" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="D76" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E76" s="15" t="s">
+      <c r="E76" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F76" s="101"/>
-      <c r="G76" s="100" t="s">
-        <v>272</v>
+      <c r="F76" s="73"/>
+      <c r="G76" s="72" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="77" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="102" t="s">
-        <v>273</v>
-      </c>
-      <c r="C77" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D77" s="23">
+      <c r="B77" s="74" t="s">
+        <v>270</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D77" s="10">
         <v>13923.94</v>
       </c>
-      <c r="E77" s="23">
+      <c r="E77" s="10">
         <v>555.54</v>
       </c>
-      <c r="G77" s="99">
+      <c r="G77" s="71">
         <f>D77-E77</f>
         <v>13368.400000000001</v>
       </c>
     </row>
     <row r="78" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="102" t="s">
+      <c r="B78" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="C78" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D78" s="23">
-        <v>1</v>
-      </c>
-      <c r="E78" s="23">
-        <v>1</v>
+      <c r="C78" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D78" s="10">
+        <v>10</v>
+      </c>
+      <c r="E78" s="10">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="96" t="s">
-        <v>276</v>
-      </c>
-      <c r="C79" s="103" t="s">
-        <v>275</v>
-      </c>
-      <c r="D79" s="20">
+      <c r="B79" s="69" t="s">
+        <v>273</v>
+      </c>
+      <c r="C79" s="75" t="s">
+        <v>272</v>
+      </c>
+      <c r="D79" s="7">
         <f>D77/D78</f>
+        <v>1392.394</v>
+      </c>
+      <c r="E79" s="7">
+        <f>E77/E78</f>
+        <v>55.553999999999995</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="74" t="s">
+        <v>271</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D80" s="10">
         <v>13923.94</v>
       </c>
-      <c r="E79" s="20">
-        <f>E77/E78</f>
+      <c r="E80" s="10">
         <v>555.54</v>
       </c>
     </row>
-    <row r="80" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="102" t="s">
-        <v>274</v>
-      </c>
-      <c r="C80" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D80" s="23">
-        <v>1455.4</v>
-      </c>
-      <c r="E80" s="23">
-        <v>555.54</v>
-      </c>
-    </row>
     <row r="81" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="27" t="s">
+      <c r="B81" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C81" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D81" s="29">
+      <c r="C81" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D81" s="16">
         <v>0.08</v>
       </c>
-      <c r="E81" s="29">
+      <c r="E81" s="16">
         <v>2.27</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
+      <c r="B83" s="103"/>
+      <c r="C83" s="103"/>
+      <c r="D83" s="103"/>
+      <c r="E83" s="103"/>
+      <c r="F83" s="103"/>
+      <c r="G83" s="103"/>
+      <c r="H83" s="103"/>
+      <c r="I83" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="S1:W2"/>
-    <mergeCell ref="S3:W3"/>
-    <mergeCell ref="S5:W5"/>
-    <mergeCell ref="S16:W16"/>
-    <mergeCell ref="S18:W18"/>
-    <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="M29:Q29"/>
-    <mergeCell ref="M39:Q39"/>
-    <mergeCell ref="M46:Q46"/>
-    <mergeCell ref="M1:Q2"/>
-    <mergeCell ref="M3:Q3"/>
-    <mergeCell ref="G1:K2"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B50:E50"/>
     <mergeCell ref="B75:E75"/>
     <mergeCell ref="A83:I83"/>
@@ -4836,11 +4816,27 @@
     <mergeCell ref="G20:K20"/>
     <mergeCell ref="G22:K22"/>
     <mergeCell ref="G32:K32"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="G1:K2"/>
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B1:E2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="M29:Q29"/>
+    <mergeCell ref="M39:Q39"/>
+    <mergeCell ref="M46:Q46"/>
+    <mergeCell ref="M1:Q2"/>
+    <mergeCell ref="M3:Q3"/>
+    <mergeCell ref="S1:W2"/>
+    <mergeCell ref="S3:W3"/>
+    <mergeCell ref="S5:W5"/>
+    <mergeCell ref="S16:W16"/>
+    <mergeCell ref="S18:W18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4852,422 +4848,436 @@
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" style="14" customWidth="1"/>
-    <col min="2" max="2" width="34" style="14" customWidth="1"/>
-    <col min="3" max="3" width="6" style="14" customWidth="1"/>
-    <col min="4" max="5" width="18" style="14" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="4" style="14" customWidth="1"/>
+    <col min="1" max="1" width="3" style="1" customWidth="1"/>
+    <col min="2" max="2" width="34" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6" style="1" customWidth="1"/>
+    <col min="4" max="5" width="18" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="4" style="1" customWidth="1"/>
     <col min="8" max="8" width="74.7109375" customWidth="1"/>
     <col min="9" max="9" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="94" t="s">
-        <v>267</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="99" t="s">
+        <v>264</v>
+      </c>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
     </row>
     <row r="2" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
     </row>
     <row r="3" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="103" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+    </row>
+    <row r="5" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="89" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+    </row>
+    <row r="6" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="5" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="95" t="s">
-        <v>279</v>
-      </c>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-    </row>
-    <row r="6" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="15" t="s">
+      <c r="G6" s="72"/>
+      <c r="H6" s="72" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="G6" s="100"/>
-      <c r="H6" s="100" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" s="64" t="s">
+      <c r="C7" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="7">
         <v>5784.15</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="7">
         <v>0</v>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="34">
         <f>D7/D11</f>
         <v>0.18433129057238734</v>
       </c>
       <c r="H7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="C8" s="65" t="s">
+      <c r="B8" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="10">
         <v>7858.35</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="10">
         <v>1817.33</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="26">
         <f>D8/D11</f>
         <v>0.25043261279004181</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="C9" s="64" t="s">
+      <c r="B9" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="7">
         <v>13261.46</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="7">
         <v>2276.65</v>
       </c>
-      <c r="F9" s="106">
+      <c r="F9" s="76">
         <f>D9/D11</f>
         <v>0.42262078899649769</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="C10" s="65" t="s">
+      <c r="B10" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C10" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="10">
         <v>4475.1400000000003</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="10">
         <v>16496.310000000001</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="26">
         <f>D10/D11</f>
         <v>0.14261530764107322</v>
       </c>
       <c r="H10" t="s">
-        <v>281</v>
-      </c>
-      <c r="I10" s="98">
+        <v>278</v>
+      </c>
+      <c r="I10" s="70">
         <f>E10-D10</f>
         <v>12021.170000000002</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="C11" s="66" t="s">
+      <c r="B11" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="13">
         <f>SUM(D7:D10)</f>
         <v>31379.1</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="13">
         <f>SUM(E7:E10)</f>
         <v>20590.29</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="35">
         <f>D11/D11</f>
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="92"/>
-      <c r="C12" s="92"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="92"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
     </row>
     <row r="14" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="95" t="s">
-        <v>282</v>
-      </c>
-      <c r="C14" s="81"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
+      <c r="B14" s="89" t="s">
+        <v>279</v>
+      </c>
+      <c r="C14" s="101"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="101"/>
     </row>
     <row r="15" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="C16" s="64" t="s">
+      <c r="C16" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="7">
         <v>359.79</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="7">
         <v>-37.590000000000003</v>
       </c>
-      <c r="F16" s="67">
+      <c r="F16" s="54">
         <f>D16/D7</f>
         <v>6.2202743704779448E-2</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="C17" s="65" t="s">
+      <c r="B17" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="10">
         <v>19.29</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="10">
         <v>86.54</v>
       </c>
-      <c r="F17" s="67">
+      <c r="F17" s="54">
         <f>D17/D8</f>
         <v>2.4547137757926279E-3</v>
       </c>
       <c r="H17" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="C18" s="64" t="s">
+      <c r="B18" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C18" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="D18" s="113">
+      <c r="D18" s="82">
         <v>1001.91</v>
       </c>
-      <c r="E18" s="113">
+      <c r="E18" s="82">
         <v>1144.69</v>
       </c>
-      <c r="F18" s="67">
-        <f t="shared" ref="F17:F20" si="0">D18/D9</f>
+      <c r="F18" s="54">
+        <f t="shared" ref="F18" si="0">D18/D9</f>
         <v>7.5550504997187337E-2</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="C19" s="65" t="s">
+      <c r="B19" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C19" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="10">
         <v>468.96</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="10">
         <v>555.24</v>
       </c>
-      <c r="F19" s="67">
+      <c r="F19" s="54">
         <f>D19/D10</f>
         <v>0.10479225230942495</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="81">
+        <v>-688.47</v>
+      </c>
+      <c r="E20" s="81">
+        <v>-487.22</v>
+      </c>
+      <c r="F20" s="80" t="s">
+        <v>215</v>
+      </c>
+      <c r="H20" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C21" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="112">
-        <v>-688.47</v>
-      </c>
-      <c r="E20" s="112">
-        <v>-487.22</v>
-      </c>
-      <c r="F20" s="111" t="s">
-        <v>217</v>
-      </c>
-      <c r="H20" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="C21" s="66" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" s="109">
+      <c r="D21" s="78">
         <f>SUM(D16:D20)</f>
         <v>1161.48</v>
       </c>
-      <c r="E21" s="109">
+      <c r="E21" s="78">
         <f>SUM(E16:E20)</f>
         <v>1261.6600000000001</v>
       </c>
-      <c r="F21" s="110" t="s">
+      <c r="F21" s="79" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="85"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="85"/>
+    </row>
+    <row r="24" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="112" t="s">
+        <v>280</v>
+      </c>
+      <c r="C24" s="90"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="90"/>
+      <c r="F24" s="90"/>
+    </row>
+    <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="101" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="92"/>
-    </row>
-    <row r="24" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="107" t="s">
-        <v>283</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="81" t="s">
+      <c r="C25" s="101"/>
+      <c r="D25" s="113" t="s">
+        <v>218</v>
+      </c>
+      <c r="E25" s="113"/>
+      <c r="F25" s="113"/>
+      <c r="H25" s="68" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="114" t="s">
         <v>219</v>
       </c>
-      <c r="C25" s="81"/>
-      <c r="D25" s="93" t="s">
+      <c r="C26" s="114"/>
+      <c r="D26" s="115" t="s">
         <v>220</v>
       </c>
-      <c r="E25" s="93"/>
-      <c r="F25" s="93"/>
-    </row>
-    <row r="26" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="83" t="s">
+      <c r="E26" s="115"/>
+      <c r="F26" s="115"/>
+    </row>
+    <row r="27" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="107" t="s">
         <v>221</v>
       </c>
-      <c r="C26" s="83"/>
-      <c r="D26" s="84" t="s">
+      <c r="C27" s="107"/>
+      <c r="D27" s="108" t="s">
         <v>222</v>
       </c>
-      <c r="E26" s="84"/>
-      <c r="F26" s="84"/>
-    </row>
-    <row r="27" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="85" t="s">
+      <c r="E27" s="108"/>
+      <c r="F27" s="108"/>
+    </row>
+    <row r="28" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="109" t="s">
         <v>223</v>
       </c>
-      <c r="C27" s="85"/>
-      <c r="D27" s="86" t="s">
+      <c r="C28" s="109"/>
+      <c r="D28" s="110" t="s">
         <v>224</v>
       </c>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
-    </row>
-    <row r="28" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="87" t="s">
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
+      <c r="H28" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="107" t="s">
         <v>225</v>
       </c>
-      <c r="C28" s="87"/>
-      <c r="D28" s="88" t="s">
+      <c r="C29" s="107"/>
+      <c r="D29" s="111" t="s">
+        <v>286</v>
+      </c>
+      <c r="E29" s="108"/>
+      <c r="F29" s="108"/>
+    </row>
+    <row r="30" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="105" t="s">
         <v>226</v>
       </c>
-      <c r="E28" s="88"/>
-      <c r="F28" s="88"/>
-      <c r="H28" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="85" t="s">
+      <c r="C30" s="105"/>
+      <c r="D30" s="106" t="s">
         <v>227</v>
       </c>
-      <c r="C29" s="85"/>
-      <c r="D29" s="114" t="s">
-        <v>289</v>
-      </c>
-      <c r="E29" s="86"/>
-      <c r="F29" s="86"/>
-    </row>
-    <row r="30" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="89" t="s">
-        <v>228</v>
-      </c>
-      <c r="C30" s="89"/>
-      <c r="D30" s="90" t="s">
-        <v>229</v>
-      </c>
-      <c r="E30" s="90"/>
-      <c r="F30" s="90"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="106"/>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="92"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="92"/>
-      <c r="G32" s="92"/>
-      <c r="H32" s="92"/>
-      <c r="I32" s="92"/>
+      <c r="A32" s="85"/>
+      <c r="B32" s="85"/>
+      <c r="C32" s="85"/>
+      <c r="D32" s="85"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="85"/>
+      <c r="G32" s="85"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B1:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="A32:I32"/>
@@ -5277,17 +5287,6 @@
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="D29:F29"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="B1:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B14:F14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -5299,110 +5298,110 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3" style="14" customWidth="1"/>
-    <col min="2" max="2" width="16" style="14" customWidth="1"/>
-    <col min="3" max="3" width="155.140625" style="14" customWidth="1"/>
-    <col min="4" max="4" width="4" style="14" customWidth="1"/>
+    <col min="1" max="1" width="3" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
+    <col min="3" max="3" width="155.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="4" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="94" t="s">
-        <v>284</v>
-      </c>
-      <c r="C1" s="1"/>
+      <c r="B1" s="99" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1" s="100"/>
     </row>
     <row r="2" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
     </row>
     <row r="3" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
     </row>
     <row r="5" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="69" t="s">
-        <v>230</v>
-      </c>
-      <c r="C5" s="108" t="s">
-        <v>231</v>
+      <c r="B5" s="56" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="77" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="70" t="s">
-        <v>232</v>
-      </c>
-      <c r="C7" s="71" t="s">
-        <v>233</v>
+      <c r="B7" s="57" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="70" t="s">
-        <v>234</v>
-      </c>
-      <c r="C9" s="71" t="s">
-        <v>235</v>
+      <c r="B9" s="57" t="s">
+        <v>232</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="72" t="s">
-        <v>236</v>
-      </c>
-      <c r="C11" s="73" t="s">
-        <v>237</v>
+      <c r="B11" s="59" t="s">
+        <v>234</v>
+      </c>
+      <c r="C11" s="60" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="74" t="s">
-        <v>238</v>
-      </c>
-      <c r="C13" s="75" t="s">
-        <v>239</v>
+      <c r="B13" s="61" t="s">
+        <v>236</v>
+      </c>
+      <c r="C13" s="62" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="76" t="s">
-        <v>240</v>
-      </c>
-      <c r="C15" s="77" t="s">
-        <v>241</v>
+      <c r="B15" s="63" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" s="64" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="74" t="s">
-        <v>242</v>
-      </c>
-      <c r="C17" s="75" t="s">
-        <v>243</v>
+      <c r="B17" s="61" t="s">
+        <v>240</v>
+      </c>
+      <c r="C17" s="62" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="78" t="s">
-        <v>244</v>
-      </c>
-      <c r="C19" s="79" t="s">
-        <v>245</v>
+      <c r="B19" s="65" t="s">
+        <v>242</v>
+      </c>
+      <c r="C19" s="66" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/myprojects/GUJTLRM/Gujarat_Toolroom_Investment_Analysis.xlsx
+++ b/myprojects/GUJTLRM/Gujarat_Toolroom_Investment_Analysis.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="900" windowWidth="21570" windowHeight="9435" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="1800" windowWidth="21570" windowHeight="9435" tabRatio="500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="HOME" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="296">
   <si>
     <t>GUJARAT TOOLROOM LIMITED</t>
   </si>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>Face Value per Share</t>
-  </si>
-  <si>
-    <t>₹ 1/-</t>
   </si>
   <si>
     <t>Financial Year</t>
@@ -766,14 +763,6 @@
 4. No dividend policy = all profits reinvested = compounding growth potential for long-term investors.</t>
   </si>
   <si>
-    <t>🏆 FP&amp;A SUMMARY</t>
-  </si>
-  <si>
-    <t>Gujarat Toolroom is in a HIGH GROWTH, HIGH RISK, MARGIN PRESSURE phase.
-Anyone can see revenue grew 52%. The FP&amp;A insight is: YES revenue grew, but cash didn't — because working capital exploded. The company is betting big on receivables turning into cash. If that happens → strong cash flows in FY26. If not → liquidity stress.
-Key metric to track: Trade Receivables collection rate. If DSO (Days Sales Outstanding) falls in FY26, this is a VERY positive sign.</t>
-  </si>
-  <si>
     <t>Gujarat Toolroom Limited (BSE: GUJTLRM | Scrip: 513337) was incorporated in 1983. It is listed on the Bombay Stock Exchange (BSE). The company's registered office is in Ahmedabad, Gujarat.</t>
   </si>
   <si>
@@ -916,19 +905,43 @@
   </si>
   <si>
     <t>FY24 Purchases exceeded Revenue because the company was building up inventory (Change in Inventories = -₹6,010 Lakhs). The excess purchases went into closing stock, not sales.</t>
+  </si>
+  <si>
+    <t>Case Study</t>
+  </si>
+  <si>
+    <t>https://tontufmoney-news.blogspot.com/2026/03/zero-promoters-negative-cash-flow-and.html</t>
+  </si>
+  <si>
+    <t>https://tontufmoney-news.blogspot.com/2026/03/cheap-for-reason-why-low-pe-ratio-can.html</t>
+  </si>
+  <si>
+    <t>Model made by Anjani Kumar Mishra | inakm.github.io | Linkedin.com/in/inakmm</t>
+  </si>
+  <si>
+    <t>₹ 10/-</t>
+  </si>
+  <si>
+    <t>🏆 SUMMARY</t>
+  </si>
+  <si>
+    <t>Gujarat Toolroom is in a HIGH GROWTH, HIGH RISK, MARGIN PRESSURE phase. 
+Anyone can see revenue grew 52%. The insight is: YES revenue grew, but cash didn't — because working capital exploded. The company is betting big on receivables turning into cash. If that happens → strong cash flows in FY26. If not → liquidity stress.
+Key metric to track: Trade Receivables collection rate. If DSO (Days Sales Outstanding) falls in FY26, this is a VERY positive sign. Also read case studies linked in HOME tab.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.00;\(#,##0.00\);\-"/>
     <numFmt numFmtId="165" formatCode="0.00%;\(0.00%\);\-"/>
     <numFmt numFmtId="166" formatCode="0.00;\(0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="0;\(0\);\-"/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1060,12 +1073,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF843C0C"/>
@@ -1136,13 +1143,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -1165,6 +1165,27 @@
     <font>
       <sz val="9"/>
       <color rgb="FF843C0C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1277,13 +1298,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1441,10 +1463,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1453,62 +1475,56 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="12" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="24" fillId="12" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="35" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="33" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="13" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="25" fillId="13" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="12" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="12" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1518,7 +1534,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1527,7 +1543,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1548,58 +1564,55 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1608,10 +1621,28 @@
     <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="4" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
     <cellStyle name="Good" xfId="2" builtinId="26"/>
+    <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -1887,324 +1918,341 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="94" t="s">
+      <c r="B1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
     </row>
     <row r="2" spans="2:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
     </row>
     <row r="3" spans="2:8" ht="6.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="94"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
     </row>
     <row r="4" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="95"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
     </row>
     <row r="5" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="96" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
+      <c r="B5" s="117" t="s">
+        <v>292</v>
+      </c>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
     </row>
     <row r="7" spans="2:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="97" t="s">
-        <v>274</v>
-      </c>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
+      <c r="B7" s="94" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
     </row>
     <row r="8" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="93" t="s">
+      <c r="B8" s="91" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+    </row>
+    <row r="9" spans="2:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="90" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="90"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="90"/>
+    </row>
+    <row r="10" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="90" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="90"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="90"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="90"/>
+    </row>
+    <row r="12" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="91" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+    </row>
+    <row r="13" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="89" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="89"/>
+      <c r="D13" s="89"/>
+      <c r="E13" s="89"/>
+      <c r="F13" s="89"/>
+      <c r="G13" s="89"/>
+      <c r="H13" s="89"/>
+    </row>
+    <row r="14" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="89" t="s">
         <v>245</v>
       </c>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-    </row>
-    <row r="9" spans="2:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="92" t="s">
+      <c r="C14" s="89"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="89"/>
+    </row>
+    <row r="15" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="89" t="s">
         <v>244</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="92"/>
-    </row>
-    <row r="10" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="92" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="92"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="92"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="92"/>
-    </row>
-    <row r="12" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-    </row>
-    <row r="13" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="91" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-    </row>
-    <row r="14" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="91" t="s">
-        <v>248</v>
-      </c>
-      <c r="C14" s="91"/>
-      <c r="D14" s="91"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-    </row>
-    <row r="15" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="91" t="s">
-        <v>247</v>
-      </c>
-      <c r="C15" s="91"/>
-      <c r="D15" s="91"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="91"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
     </row>
     <row r="16" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="91" t="s">
-        <v>246</v>
-      </c>
-      <c r="C16" s="91"/>
-      <c r="D16" s="91"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="91"/>
-      <c r="G16" s="91"/>
-      <c r="H16" s="91"/>
+      <c r="B16" s="89" t="s">
+        <v>243</v>
+      </c>
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="89"/>
+      <c r="H16" s="89"/>
     </row>
     <row r="17" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="91" t="s">
+      <c r="B17" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="91"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
+      <c r="C17" s="89"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="91"/>
-      <c r="C18" s="91"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="91"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="89"/>
     </row>
     <row r="19" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="86" t="s">
+      <c r="B19" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="87"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="87"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="85"/>
     </row>
     <row r="20" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="88"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="88"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="88"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="86"/>
     </row>
     <row r="21" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="89"/>
-      <c r="D21" s="89"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="87"/>
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="90" t="s">
+      <c r="B22" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="90"/>
+      <c r="C22" s="88"/>
       <c r="D22" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="83"/>
+      <c r="C23" s="81"/>
       <c r="D23" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="84" t="s">
+      <c r="B24" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="84"/>
+      <c r="C24" s="82"/>
       <c r="D24" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="83"/>
+      <c r="C25" s="81"/>
       <c r="D25" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="84" t="s">
+      <c r="B26" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="84"/>
+      <c r="C26" s="82"/>
       <c r="D26" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="83" t="s">
+      <c r="B27" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="83"/>
-      <c r="D27" s="3" t="s">
+      <c r="C27" s="81"/>
+      <c r="D27" s="116" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="82" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="28" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="84" t="s">
+      <c r="C28" s="82"/>
+      <c r="D28" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="84"/>
-      <c r="D28" s="4" t="s">
+    </row>
+    <row r="29" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="81" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="29" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="83" t="s">
+      <c r="C29" s="81"/>
+      <c r="D29" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="83"/>
-      <c r="D29" s="3" t="s">
+    </row>
+    <row r="30" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="82" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="84" t="s">
+      <c r="C30" s="82"/>
+      <c r="D30" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="84"/>
-      <c r="D30" s="4" t="s">
+    </row>
+    <row r="31" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="81" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="31" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="83" t="s">
+      <c r="C31" s="81"/>
+      <c r="D31" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="83"/>
-      <c r="D31" s="3" t="s">
+    </row>
+    <row r="32" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="82" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="32" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="84" t="s">
+      <c r="C32" s="82"/>
+      <c r="D32" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="84"/>
-      <c r="D32" s="4" t="s">
-        <v>30</v>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B33" s="114" t="s">
+        <v>289</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="115" t="s">
+        <v>291</v>
+      </c>
+      <c r="H33" s="1">
+        <v>2</v>
+      </c>
+      <c r="I33" s="115" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="85"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="85"/>
-      <c r="D34" s="85"/>
-      <c r="E34" s="85"/>
-      <c r="F34" s="85"/>
-      <c r="G34" s="85"/>
-      <c r="H34" s="85"/>
-      <c r="I34" s="85"/>
+      <c r="A34" s="83"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -2239,8 +2287,12 @@
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="A34:I34"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D33" r:id="rId1"/>
+    <hyperlink ref="I33" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2272,90 +2324,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="G1" s="100" t="s">
-        <v>251</v>
-      </c>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
+      <c r="B1" s="97" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="G1" s="97" t="s">
+        <v>248</v>
+      </c>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
       <c r="L1" s="1"/>
-      <c r="M1" s="100" t="s">
+      <c r="M1" s="97" t="s">
+        <v>254</v>
+      </c>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="96" t="s">
+        <v>265</v>
+      </c>
+      <c r="T1" s="97"/>
+      <c r="U1" s="97"/>
+      <c r="V1" s="97"/>
+      <c r="W1" s="97"/>
+    </row>
+    <row r="2" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="97"/>
+      <c r="V2" s="97"/>
+      <c r="W2" s="97"/>
+    </row>
+    <row r="3" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="99" t="s">
         <v>257</v>
       </c>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="100"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="99" t="s">
-        <v>268</v>
-      </c>
-      <c r="T1" s="100"/>
-      <c r="U1" s="100"/>
-      <c r="V1" s="100"/>
-      <c r="W1" s="100"/>
-    </row>
-    <row r="2" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
-      <c r="O2" s="100"/>
-      <c r="P2" s="100"/>
-      <c r="Q2" s="100"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="100"/>
-      <c r="T2" s="100"/>
-      <c r="U2" s="100"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-    </row>
-    <row r="3" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="102" t="s">
-        <v>260</v>
-      </c>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
+      <c r="O3" s="99"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="99"/>
       <c r="R3" s="1"/>
-      <c r="S3" s="85"/>
-      <c r="T3" s="85"/>
-      <c r="U3" s="85"/>
-      <c r="V3" s="85"/>
-      <c r="W3" s="85"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="83"/>
+      <c r="U3" s="83"/>
+      <c r="V3" s="83"/>
+      <c r="W3" s="83"/>
     </row>
     <row r="4" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -2370,14 +2422,14 @@
       <c r="W4" s="1"/>
     </row>
     <row r="5" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="90" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
+      <c r="B5" s="88" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
       <c r="G5" s="20" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
@@ -2385,88 +2437,88 @@
       <c r="K5" s="20"/>
       <c r="L5" s="1"/>
       <c r="M5" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N5" s="20"/>
       <c r="O5" s="20"/>
       <c r="P5" s="20"/>
       <c r="Q5" s="20"/>
       <c r="R5" s="1"/>
-      <c r="S5" s="89" t="s">
-        <v>275</v>
-      </c>
-      <c r="T5" s="101"/>
-      <c r="U5" s="101"/>
-      <c r="V5" s="101"/>
-      <c r="W5" s="101"/>
+      <c r="S5" s="87" t="s">
+        <v>272</v>
+      </c>
+      <c r="T5" s="98"/>
+      <c r="U5" s="98"/>
+      <c r="V5" s="98"/>
+      <c r="W5" s="98"/>
     </row>
     <row r="6" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="Q6" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="T6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="W6" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" s="7">
         <v>31379.09</v>
@@ -2476,10 +2528,10 @@
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="I7" s="23">
         <f>D7</f>
@@ -2489,16 +2541,16 @@
         <f>E7</f>
         <v>20590.29</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="65">
         <f>(I7-J7)/J7</f>
         <v>0.52397513585287037</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N7" s="36" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O7" s="24">
         <f>I16</f>
@@ -2509,14 +2561,14 @@
         <v>6.1274027709177482E-2</v>
       </c>
       <c r="Q7" s="37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U7" s="43">
         <f>D36</f>
@@ -2533,10 +2585,10 @@
     </row>
     <row r="8" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" s="10">
         <v>34.97</v>
@@ -2546,10 +2598,10 @@
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I8" s="25">
         <f>D9</f>
@@ -2559,16 +2611,16 @@
         <f>E9</f>
         <v>20742.57</v>
       </c>
-      <c r="K8" s="67">
+      <c r="K8" s="65">
         <f>(I8-J8)/J8</f>
         <v>0.51447289318536715</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N8" s="38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O8" s="26">
         <f>I18</f>
@@ -2579,14 +2631,14 @@
         <v>8.4937123275097184E-2</v>
       </c>
       <c r="Q8" s="39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U8" s="44">
         <f>D47</f>
@@ -2603,10 +2655,10 @@
     </row>
     <row r="9" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="13">
         <f>D8+D7</f>
@@ -2618,10 +2670,10 @@
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I9" s="23">
         <f>D21</f>
@@ -2631,16 +2683,16 @@
         <f>E21</f>
         <v>1261.6500000000001</v>
       </c>
-      <c r="K9" s="67">
+      <c r="K9" s="65">
         <f>(I9-J9)/J9</f>
         <v>-7.9396029009630303E-2</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="N9" s="36" t="s">
         <v>125</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>126</v>
       </c>
       <c r="O9" s="34">
         <f>I19</f>
@@ -2651,14 +2703,14 @@
         <v>8.4907011994488815E-2</v>
       </c>
       <c r="Q9" s="37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="T9" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U9" s="48">
         <f>U7-U8</f>
@@ -2675,10 +2727,10 @@
     </row>
     <row r="10" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="10">
         <v>24048.83</v>
@@ -2688,10 +2740,10 @@
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I10" s="25">
         <f>D16</f>
@@ -2701,16 +2753,16 @@
         <f>E16</f>
         <v>18994.589999999997</v>
       </c>
-      <c r="K10" s="67">
+      <c r="K10" s="65">
         <f>(I10-J10)/J10</f>
         <v>0.57253407417585767</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="N10" s="38" t="s">
         <v>128</v>
-      </c>
-      <c r="N10" s="38" t="s">
-        <v>129</v>
       </c>
       <c r="O10" s="26">
         <f>D21/D41</f>
@@ -2721,7 +2773,7 @@
         <v>0.66508695445895305</v>
       </c>
       <c r="Q10" s="39" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -2732,10 +2784,10 @@
     </row>
     <row r="11" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="10">
         <v>5480.32</v>
@@ -2746,10 +2798,10 @@
       <c r="F11" s="8"/>
       <c r="L11" s="1"/>
       <c r="M11" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="N11" s="36" t="s">
         <v>131</v>
-      </c>
-      <c r="N11" s="36" t="s">
-        <v>132</v>
       </c>
       <c r="O11" s="34">
         <f>D21/D37</f>
@@ -2760,14 +2812,14 @@
         <v>0.12595314680707051</v>
       </c>
       <c r="Q11" s="37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R11" s="1"/>
-      <c r="S11" s="69" t="s">
-        <v>267</v>
+      <c r="S11" s="67" t="s">
+        <v>264</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U11" s="45">
         <f>D32</f>
@@ -2784,10 +2836,10 @@
     </row>
     <row r="12" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D12" s="10">
         <v>39.909999999999997</v>
@@ -2796,17 +2848,17 @@
         <v>28.26</v>
       </c>
       <c r="F12" s="8"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-      <c r="J12" s="85"/>
-      <c r="K12" s="85"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="83"/>
+      <c r="K12" s="83"/>
       <c r="L12" s="1"/>
       <c r="M12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="N12" s="38" t="s">
         <v>134</v>
-      </c>
-      <c r="N12" s="38" t="s">
-        <v>135</v>
       </c>
       <c r="O12" s="26">
         <f>(D17+D13)/(D37-D47)</f>
@@ -2817,14 +2869,14 @@
         <v>0.92161142037786981</v>
       </c>
       <c r="Q12" s="39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R12" s="1"/>
       <c r="S12" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U12" s="44">
         <f>D31</f>
@@ -2841,10 +2893,10 @@
     </row>
     <row r="13" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" s="10">
         <v>4.4400000000000004</v>
@@ -2861,10 +2913,10 @@
       <c r="L13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U13" s="45">
         <f>D33</f>
@@ -2881,10 +2933,10 @@
     </row>
     <row r="14" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" s="10">
         <v>41.89</v>
@@ -2893,16 +2945,16 @@
         <v>3.23</v>
       </c>
       <c r="F14" s="8"/>
-      <c r="G14" s="101" t="s">
-        <v>255</v>
-      </c>
-      <c r="H14" s="101"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="101"/>
-      <c r="K14" s="101"/>
+      <c r="G14" s="98" t="s">
+        <v>252</v>
+      </c>
+      <c r="H14" s="98"/>
+      <c r="I14" s="98"/>
+      <c r="J14" s="98"/>
+      <c r="K14" s="98"/>
       <c r="L14" s="1"/>
       <c r="M14" s="20" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="N14" s="20"/>
       <c r="O14" s="20"/>
@@ -2910,10 +2962,10 @@
       <c r="Q14" s="20"/>
       <c r="R14" s="1"/>
       <c r="S14" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U14" s="44">
         <f>D44</f>
@@ -2930,10 +2982,10 @@
     </row>
     <row r="15" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" s="10">
         <v>254.25</v>
@@ -2943,42 +2995,42 @@
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="Q15" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U15" s="45">
         <f>D43</f>
@@ -2995,10 +3047,10 @@
     </row>
     <row r="16" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" s="13">
         <f>SUM(D10:D15)</f>
@@ -3010,16 +3062,16 @@
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="I16" s="67">
+      <c r="I16" s="65">
         <f>D21/D7</f>
         <v>3.7014457716906389E-2</v>
       </c>
-      <c r="J16" s="67">
+      <c r="J16" s="65">
         <f>E21/E7</f>
         <v>6.1274027709177482E-2</v>
       </c>
@@ -3029,10 +3081,10 @@
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="N16" s="36" t="s">
         <v>137</v>
-      </c>
-      <c r="N16" s="36" t="s">
-        <v>138</v>
       </c>
       <c r="O16" s="40">
         <f>D36/D47</f>
@@ -3043,21 +3095,21 @@
         <v>1.2107142241368694</v>
       </c>
       <c r="Q16" s="37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R16" s="1"/>
-      <c r="S16" s="85"/>
-      <c r="T16" s="85"/>
-      <c r="U16" s="85"/>
-      <c r="V16" s="85"/>
-      <c r="W16" s="85"/>
+      <c r="S16" s="83"/>
+      <c r="T16" s="83"/>
+      <c r="U16" s="83"/>
+      <c r="V16" s="83"/>
+      <c r="W16" s="83"/>
     </row>
     <row r="17" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" s="16">
         <f>D9-D16</f>
@@ -3069,10 +3121,10 @@
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I17" s="28">
         <f>D17/D9</f>
@@ -3088,10 +3140,10 @@
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="N17" s="38" t="s">
         <v>140</v>
-      </c>
-      <c r="N17" s="38" t="s">
-        <v>141</v>
       </c>
       <c r="O17" s="41">
         <f>(D33+D32)/D47</f>
@@ -3102,16 +3154,16 @@
         <v>0.1296537132413613</v>
       </c>
       <c r="Q17" s="39" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="R17" s="1"/>
     </row>
     <row r="18" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18" s="10">
         <v>389.01</v>
@@ -3121,10 +3173,10 @@
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I18" s="27">
         <f>(D7-D11-D10)/D7</f>
@@ -3140,10 +3192,10 @@
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="N18" s="36" t="s">
         <v>143</v>
-      </c>
-      <c r="N18" s="36" t="s">
-        <v>144</v>
       </c>
       <c r="O18" s="42">
         <f>D33/D47</f>
@@ -3154,21 +3206,21 @@
         <v>9.672580561733822E-2</v>
       </c>
       <c r="Q18" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R18" s="1"/>
-      <c r="S18" s="85"/>
-      <c r="T18" s="85"/>
-      <c r="U18" s="85"/>
-      <c r="V18" s="85"/>
-      <c r="W18" s="85"/>
+      <c r="S18" s="83"/>
+      <c r="T18" s="83"/>
+      <c r="U18" s="83"/>
+      <c r="V18" s="83"/>
+      <c r="W18" s="83"/>
     </row>
     <row r="19" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" s="10">
         <v>6.08</v>
@@ -3178,10 +3230,10 @@
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I19" s="28">
         <f>(D17+D13)/D7</f>
@@ -3200,10 +3252,10 @@
     </row>
     <row r="20" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" s="13">
         <f>SUM(D18:D19)</f>
@@ -3214,20 +3266,20 @@
         <v>482.47999999999996</v>
       </c>
       <c r="F20" s="8"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="85"/>
-      <c r="J20" s="85"/>
-      <c r="K20" s="85"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="83"/>
       <c r="L20" s="1"/>
       <c r="R20" s="1"/>
     </row>
     <row r="21" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" s="19">
         <v>1161.48</v>
@@ -3250,74 +3302,74 @@
       <c r="R21" s="1"/>
     </row>
     <row r="22" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
       <c r="F22" s="8"/>
-      <c r="G22" s="101" t="s">
-        <v>256</v>
-      </c>
-      <c r="H22" s="101"/>
-      <c r="I22" s="101"/>
-      <c r="J22" s="101"/>
-      <c r="K22" s="101"/>
+      <c r="G22" s="98" t="s">
+        <v>253</v>
+      </c>
+      <c r="H22" s="98"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="98"/>
+      <c r="K22" s="98"/>
       <c r="L22" s="1"/>
-      <c r="M22" s="101" t="s">
-        <v>262</v>
-      </c>
-      <c r="N22" s="101"/>
-      <c r="O22" s="101"/>
-      <c r="P22" s="101"/>
-      <c r="Q22" s="101"/>
+      <c r="M22" s="98" t="s">
+        <v>259</v>
+      </c>
+      <c r="N22" s="98"/>
+      <c r="O22" s="98"/>
+      <c r="P22" s="98"/>
+      <c r="Q22" s="98"/>
       <c r="R22" s="1"/>
     </row>
     <row r="23" spans="2:23" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="N23" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="O23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q23" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="O23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="R23" s="1"/>
     </row>
     <row r="24" spans="2:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="90" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
+      <c r="B24" s="88" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="88"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
       <c r="G24" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I24" s="23">
         <f t="shared" ref="I24:J29" si="0">D10</f>
@@ -3333,10 +3385,10 @@
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="N24" s="36" t="s">
         <v>146</v>
-      </c>
-      <c r="N24" s="36" t="s">
-        <v>147</v>
       </c>
       <c r="O24" s="40">
         <f>D43/D41</f>
@@ -3347,28 +3399,28 @@
         <v>0</v>
       </c>
       <c r="Q24" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R24" s="1"/>
     </row>
     <row r="25" spans="2:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="G25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I25" s="25">
         <f t="shared" si="0"/>
@@ -3384,10 +3436,10 @@
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="N25" s="38" t="s">
         <v>149</v>
-      </c>
-      <c r="N25" s="38" t="s">
-        <v>150</v>
       </c>
       <c r="O25" s="41">
         <f>D43/D37</f>
@@ -3398,22 +3450,22 @@
         <v>0</v>
       </c>
       <c r="Q25" s="39" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R25" s="1"/>
     </row>
     <row r="26" spans="2:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="101" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
+      <c r="B26" s="98" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="98"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
       <c r="G26" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I26" s="29">
         <f t="shared" si="0"/>
@@ -3429,10 +3481,10 @@
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="N26" s="36" t="s">
         <v>152</v>
-      </c>
-      <c r="N26" s="36" t="s">
-        <v>153</v>
       </c>
       <c r="O26" s="42">
         <f>(D17+D13)/D13</f>
@@ -3443,16 +3495,16 @@
         <v>6243.7857142857247</v>
       </c>
       <c r="Q26" s="37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R26" s="1"/>
     </row>
     <row r="27" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D27" s="10">
         <v>91.63</v>
@@ -3462,10 +3514,10 @@
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I27" s="25">
         <f t="shared" si="0"/>
@@ -3481,10 +3533,10 @@
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="N27" s="38" t="s">
         <v>155</v>
-      </c>
-      <c r="N27" s="38" t="s">
-        <v>156</v>
       </c>
       <c r="O27" s="41">
         <f>D37/D41</f>
@@ -3495,16 +3547,16 @@
         <v>5.2804314248512094</v>
       </c>
       <c r="Q27" s="39" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R27" s="1"/>
     </row>
     <row r="28" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D28" s="10">
         <v>67.25</v>
@@ -3514,10 +3566,10 @@
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I28" s="29">
         <f t="shared" si="0"/>
@@ -3541,23 +3593,23 @@
     </row>
     <row r="29" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D29" s="10">
         <v>6.08</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I29" s="25">
         <f t="shared" si="0"/>
@@ -3572,21 +3624,21 @@
         <v>1.0941438102298</v>
       </c>
       <c r="L29" s="1"/>
-      <c r="M29" s="101" t="s">
-        <v>263</v>
-      </c>
-      <c r="N29" s="101"/>
-      <c r="O29" s="101"/>
-      <c r="P29" s="101"/>
-      <c r="Q29" s="101"/>
+      <c r="M29" s="98" t="s">
+        <v>260</v>
+      </c>
+      <c r="N29" s="98"/>
+      <c r="O29" s="98"/>
+      <c r="P29" s="98"/>
+      <c r="Q29" s="98"/>
       <c r="R29" s="1"/>
     </row>
     <row r="30" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30" s="13">
         <f>SUM(D27:D29)</f>
@@ -3598,10 +3650,10 @@
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I30" s="31">
         <f>SUM(I24:I29)</f>
@@ -3617,28 +3669,28 @@
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="N30" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="O30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q30" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="R30" s="1"/>
     </row>
     <row r="31" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D31" s="10">
         <v>698.71</v>
@@ -3649,10 +3701,10 @@
       <c r="F31" s="8"/>
       <c r="L31" s="1"/>
       <c r="M31" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="N31" s="36" t="s">
         <v>158</v>
-      </c>
-      <c r="N31" s="36" t="s">
-        <v>159</v>
       </c>
       <c r="O31" s="40">
         <f>D7/D37</f>
@@ -3663,16 +3715,16 @@
         <v>2.0555715286887457</v>
       </c>
       <c r="Q31" s="37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="R31" s="1"/>
     </row>
     <row r="32" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D32" s="10">
         <v>15138.64</v>
@@ -3681,19 +3733,19 @@
         <v>267.37</v>
       </c>
       <c r="F32" s="8"/>
-      <c r="G32" s="104" t="s">
-        <v>252</v>
-      </c>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
+      <c r="G32" s="101" t="s">
+        <v>249</v>
+      </c>
+      <c r="H32" s="101"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
       <c r="L32" s="1"/>
       <c r="M32" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="N32" s="38" t="s">
         <v>161</v>
-      </c>
-      <c r="N32" s="38" t="s">
-        <v>162</v>
       </c>
       <c r="O32" s="41">
         <f>D10/((E31+D31)/2)</f>
@@ -3704,16 +3756,16 @@
         <v>8.0439130413673343</v>
       </c>
       <c r="Q32" s="39" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R32" s="1"/>
     </row>
     <row r="33" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D33" s="10">
         <v>97.53</v>
@@ -3723,26 +3775,26 @@
       </c>
       <c r="F33" s="8"/>
       <c r="G33" s="33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H33" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="I33" s="33" t="s">
+      <c r="J33" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="J33" s="33" t="s">
-        <v>36</v>
-      </c>
       <c r="K33" s="33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="N33" s="36" t="s">
         <v>164</v>
-      </c>
-      <c r="N33" s="36" t="s">
-        <v>165</v>
       </c>
       <c r="O33" s="42">
         <f>D7/((E32+D32)/2)</f>
@@ -3753,16 +3805,16 @@
         <v>154.02094475820024</v>
       </c>
       <c r="Q33" s="37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R33" s="1"/>
     </row>
     <row r="34" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D34" s="10">
         <v>38521.11</v>
@@ -3772,10 +3824,10 @@
       </c>
       <c r="F34" s="8"/>
       <c r="G34" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="I34" s="30">
         <f>D10/D7</f>
@@ -3791,30 +3843,30 @@
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="N34" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="N34" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="O34" s="41">
+      <c r="O34" s="113">
         <f>365/O33</f>
         <v>89.600967555145786</v>
       </c>
-      <c r="P34" s="41">
+      <c r="P34" s="113">
         <f>365/P33</f>
         <v>2.369807564633621</v>
       </c>
       <c r="Q34" s="39" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="R34" s="1"/>
     </row>
     <row r="35" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D35" s="10">
         <v>46.84</v>
@@ -3824,10 +3876,10 @@
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I35" s="28">
         <f>D12/D7</f>
@@ -3843,10 +3895,10 @@
       </c>
       <c r="L35" s="1"/>
       <c r="M35" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="N35" s="36" t="s">
         <v>170</v>
-      </c>
-      <c r="N35" s="36" t="s">
-        <v>171</v>
       </c>
       <c r="O35" s="42">
         <f>D10/((E44+D44)/2)</f>
@@ -3857,16 +3909,16 @@
         <v>6.5595024111363616</v>
       </c>
       <c r="Q35" s="37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R35" s="1"/>
     </row>
     <row r="36" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D36" s="13">
         <f>SUM(D31:D35)</f>
@@ -3878,10 +3930,10 @@
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I36" s="30">
         <f>D15/D7</f>
@@ -3897,30 +3949,30 @@
       </c>
       <c r="L36" s="1"/>
       <c r="M36" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="N36" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="N36" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="O36" s="41">
+      <c r="O36" s="113">
         <f>365/O35</f>
         <v>153.49049829035343</v>
       </c>
-      <c r="P36" s="41">
+      <c r="P36" s="113">
         <f>365/P35</f>
         <v>55.64446464419666</v>
       </c>
       <c r="Q36" s="39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R36" s="1"/>
     </row>
     <row r="37" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D37" s="19">
         <f>D36+D30</f>
@@ -3932,10 +3984,10 @@
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I37" s="32">
         <f>D16/D7</f>
@@ -3951,10 +4003,10 @@
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="N37" s="36" t="s">
         <v>176</v>
-      </c>
-      <c r="N37" s="36" t="s">
-        <v>177</v>
       </c>
       <c r="O37" s="42">
         <f>D7/(D36-D47)</f>
@@ -3965,17 +4017,17 @@
         <v>12.034278800914107</v>
       </c>
       <c r="Q37" s="37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R37" s="1"/>
     </row>
     <row r="38" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="101" t="s">
-        <v>67</v>
-      </c>
-      <c r="C38" s="101"/>
-      <c r="D38" s="101"/>
-      <c r="E38" s="101"/>
+      <c r="B38" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" s="98"/>
+      <c r="D38" s="98"/>
+      <c r="E38" s="98"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
@@ -3986,10 +4038,10 @@
     </row>
     <row r="39" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D39" s="10">
         <v>13923.94</v>
@@ -3999,21 +4051,21 @@
       </c>
       <c r="F39" s="8"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="89" t="s">
-        <v>266</v>
-      </c>
-      <c r="N39" s="101"/>
-      <c r="O39" s="101"/>
-      <c r="P39" s="101"/>
-      <c r="Q39" s="101"/>
+      <c r="M39" s="87" t="s">
+        <v>263</v>
+      </c>
+      <c r="N39" s="98"/>
+      <c r="O39" s="98"/>
+      <c r="P39" s="98"/>
+      <c r="Q39" s="98"/>
       <c r="R39" s="1"/>
     </row>
     <row r="40" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D40" s="10">
         <v>8042.04</v>
@@ -4024,28 +4076,28 @@
       <c r="F40" s="8"/>
       <c r="L40" s="1"/>
       <c r="M40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="N40" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N40" s="2" t="s">
+      <c r="O40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q40" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q40" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="R40" s="1"/>
     </row>
     <row r="41" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D41" s="13">
         <f>SUM(D39:D40)</f>
@@ -4058,10 +4110,10 @@
       <c r="F41" s="8"/>
       <c r="L41" s="1"/>
       <c r="M41" s="21" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="N41" s="36" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O41" s="43">
         <f>D21/D80</f>
@@ -4072,16 +4124,16 @@
         <v>2.2710335889404907</v>
       </c>
       <c r="Q41" s="37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="R41" s="1"/>
     </row>
     <row r="42" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D42" s="10">
         <v>0</v>
@@ -4092,10 +4144,10 @@
       <c r="F42" s="8"/>
       <c r="L42" s="1"/>
       <c r="M42" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N42" s="38" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O42" s="44">
         <f>D41/D79</f>
@@ -4106,16 +4158,16 @@
         <v>34.146416099650793</v>
       </c>
       <c r="Q42" s="39" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="R42" s="1"/>
     </row>
     <row r="43" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D43" s="10">
         <v>6661.09</v>
@@ -4126,10 +4178,10 @@
       <c r="F43" s="8"/>
       <c r="L43" s="1"/>
       <c r="M43" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="N43" s="36" t="s">
         <v>183</v>
-      </c>
-      <c r="N43" s="36" t="s">
-        <v>184</v>
       </c>
       <c r="O43" s="45">
         <f>D62/D79</f>
@@ -4140,16 +4192,16 @@
         <v>19.127335565395832</v>
       </c>
       <c r="Q43" s="37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="R43" s="1"/>
     </row>
     <row r="44" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D44" s="10">
         <v>12648.78</v>
@@ -4160,10 +4212,10 @@
       <c r="F44" s="8"/>
       <c r="L44" s="1"/>
       <c r="M44" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="N44" s="38" t="s">
         <v>186</v>
-      </c>
-      <c r="N44" s="38" t="s">
-        <v>187</v>
       </c>
       <c r="O44" s="44">
         <f>0</f>
@@ -4174,16 +4226,16 @@
         <v>0</v>
       </c>
       <c r="Q44" s="39" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R44" s="1"/>
     </row>
     <row r="45" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D45" s="10">
         <v>389.39</v>
@@ -4202,10 +4254,10 @@
     </row>
     <row r="46" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D46" s="10">
         <v>13002.55</v>
@@ -4215,21 +4267,21 @@
       </c>
       <c r="F46" s="8"/>
       <c r="L46" s="1"/>
-      <c r="M46" s="89" t="s">
-        <v>265</v>
-      </c>
-      <c r="N46" s="101"/>
-      <c r="O46" s="101"/>
-      <c r="P46" s="101"/>
-      <c r="Q46" s="101"/>
+      <c r="M46" s="87" t="s">
+        <v>262</v>
+      </c>
+      <c r="N46" s="98"/>
+      <c r="O46" s="98"/>
+      <c r="P46" s="98"/>
+      <c r="Q46" s="98"/>
       <c r="R46" s="1"/>
     </row>
     <row r="47" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D47" s="13">
         <f>SUM(D42:D46)</f>
@@ -4242,28 +4294,28 @@
       <c r="F47" s="8"/>
       <c r="L47" s="1"/>
       <c r="M47" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="N47" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="N47" s="2" t="s">
+      <c r="O47" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q47" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="O47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q47" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="R47" s="1"/>
     </row>
     <row r="48" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D48" s="19">
         <f>D47+D41</f>
@@ -4276,10 +4328,10 @@
       <c r="F48" s="8"/>
       <c r="L48" s="1"/>
       <c r="M48" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="N48" s="36" t="s">
         <v>189</v>
-      </c>
-      <c r="N48" s="36" t="s">
-        <v>190</v>
       </c>
       <c r="O48" s="40">
         <f>D62/D21</f>
@@ -4290,17 +4342,17 @@
         <v>0.84223041255498743</v>
       </c>
       <c r="Q48" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R48" s="1"/>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.25">
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="N49" s="38" t="s">
         <v>192</v>
-      </c>
-      <c r="N49" s="38" t="s">
-        <v>193</v>
       </c>
       <c r="O49" s="26">
         <f>D62/D7</f>
@@ -4311,23 +4363,23 @@
         <v>5.1606849636406278E-2</v>
       </c>
       <c r="Q49" s="39" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R49" s="1"/>
     </row>
     <row r="50" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="90" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" s="90"/>
-      <c r="D50" s="90"/>
-      <c r="E50" s="90"/>
+      <c r="B50" s="88" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="88"/>
+      <c r="D50" s="88"/>
+      <c r="E50" s="88"/>
       <c r="L50" s="1"/>
       <c r="M50" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="N50" s="36" t="s">
         <v>195</v>
-      </c>
-      <c r="N50" s="36" t="s">
-        <v>196</v>
       </c>
       <c r="O50" s="34">
         <f>D62/D37</f>
@@ -4338,30 +4390,30 @@
         <v>0.1060815707979179</v>
       </c>
       <c r="Q50" s="37" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R50" s="1"/>
     </row>
     <row r="51" spans="2:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="52" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D52" s="22">
         <v>1544.41</v>
@@ -4373,10 +4425,10 @@
     </row>
     <row r="53" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D53" s="10">
         <v>41.89</v>
@@ -4388,10 +4440,10 @@
     </row>
     <row r="54" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D54" s="10">
         <v>4.4400000000000004</v>
@@ -4403,10 +4455,10 @@
     </row>
     <row r="55" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D55" s="13">
         <f>D52+D53+D54</f>
@@ -4420,10 +4472,10 @@
     </row>
     <row r="56" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D56" s="10">
         <v>12851.33</v>
@@ -4435,10 +4487,10 @@
     </row>
     <row r="57" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D57" s="10">
         <v>5480.32</v>
@@ -4450,10 +4502,10 @@
     </row>
     <row r="58" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D58" s="10">
         <v>5071.45</v>
@@ -4465,10 +4517,10 @@
     </row>
     <row r="59" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D59" s="10">
         <v>-14871.27</v>
@@ -4480,10 +4532,10 @@
     </row>
     <row r="60" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D60" s="10">
         <v>-35968.910000000003</v>
@@ -4495,7 +4547,7 @@
     </row>
     <row r="61" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C61" s="9" t="str">
         <f>C60</f>
@@ -4511,10 +4563,10 @@
     </row>
     <row r="62" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D62" s="16">
         <v>-26237.27</v>
@@ -4526,10 +4578,10 @@
     </row>
     <row r="63" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D63" s="10">
         <v>-14.78</v>
@@ -4541,10 +4593,10 @@
     </row>
     <row r="64" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D64" s="10">
         <v>0</v>
@@ -4556,10 +4608,10 @@
     </row>
     <row r="65" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D65" s="16">
         <v>-14.78</v>
@@ -4571,10 +4623,10 @@
     </row>
     <row r="66" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D66" s="10">
         <v>19463.060000000001</v>
@@ -4586,10 +4638,10 @@
     </row>
     <row r="67" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D67" s="10">
         <v>6661.09</v>
@@ -4601,7 +4653,7 @@
     </row>
     <row r="68" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C68" s="9" t="str">
         <f>C67</f>
@@ -4611,16 +4663,16 @@
         <v>-555.54</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F68" s="8"/>
     </row>
     <row r="69" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D69" s="10">
         <v>-4.4400000000000004</v>
@@ -4632,10 +4684,10 @@
     </row>
     <row r="70" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D70" s="16">
         <v>25564.18</v>
@@ -4647,10 +4699,10 @@
     </row>
     <row r="71" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D71" s="19">
         <f>D62+D65+D70</f>
@@ -4664,10 +4716,10 @@
     </row>
     <row r="72" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D72" s="10">
         <v>785.41</v>
@@ -4679,10 +4731,10 @@
     </row>
     <row r="73" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D73" s="19">
         <v>97.53</v>
@@ -4693,37 +4745,37 @@
       <c r="F73" s="8"/>
     </row>
     <row r="75" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="90" t="s">
-        <v>98</v>
-      </c>
-      <c r="C75" s="90"/>
-      <c r="D75" s="90"/>
-      <c r="E75" s="90"/>
+      <c r="B75" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="C75" s="88"/>
+      <c r="D75" s="88"/>
+      <c r="E75" s="88"/>
     </row>
     <row r="76" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F76" s="73"/>
-      <c r="G76" s="72" t="s">
-        <v>269</v>
+      <c r="F76" s="71"/>
+      <c r="G76" s="70" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="77" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="74" t="s">
-        <v>270</v>
+      <c r="B77" s="72" t="s">
+        <v>267</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D77" s="10">
         <v>13923.94</v>
@@ -4731,17 +4783,17 @@
       <c r="E77" s="10">
         <v>555.54</v>
       </c>
-      <c r="G77" s="71">
+      <c r="G77" s="69">
         <f>D77-E77</f>
         <v>13368.400000000001</v>
       </c>
     </row>
     <row r="78" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="74" t="s">
+      <c r="B78" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D78" s="10">
         <v>10</v>
@@ -4751,11 +4803,11 @@
       </c>
     </row>
     <row r="79" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="69" t="s">
-        <v>273</v>
-      </c>
-      <c r="C79" s="75" t="s">
-        <v>272</v>
+      <c r="B79" s="67" t="s">
+        <v>270</v>
+      </c>
+      <c r="C79" s="73" t="s">
+        <v>269</v>
       </c>
       <c r="D79" s="7">
         <f>D77/D78</f>
@@ -4767,11 +4819,11 @@
       </c>
     </row>
     <row r="80" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="74" t="s">
-        <v>271</v>
+      <c r="B80" s="72" t="s">
+        <v>268</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D80" s="10">
         <v>13923.94</v>
@@ -4782,10 +4834,10 @@
     </row>
     <row r="81" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D81" s="16">
         <v>0.08</v>
@@ -4795,17 +4847,17 @@
       </c>
     </row>
     <row r="83" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="103" t="s">
+      <c r="A83" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B83" s="103"/>
-      <c r="C83" s="103"/>
-      <c r="D83" s="103"/>
-      <c r="E83" s="103"/>
-      <c r="F83" s="103"/>
-      <c r="G83" s="103"/>
-      <c r="H83" s="103"/>
-      <c r="I83" s="103"/>
+      <c r="B83" s="100"/>
+      <c r="C83" s="100"/>
+      <c r="D83" s="100"/>
+      <c r="E83" s="100"/>
+      <c r="F83" s="100"/>
+      <c r="G83" s="100"/>
+      <c r="H83" s="100"/>
+      <c r="I83" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -4860,66 +4912,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="99" t="s">
-        <v>264</v>
-      </c>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
+      <c r="B1" s="96" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
     </row>
     <row r="2" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
     </row>
     <row r="3" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="103" t="s">
-        <v>205</v>
-      </c>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
+      <c r="B3" s="100" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="100"/>
     </row>
     <row r="5" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="89" t="s">
-        <v>276</v>
-      </c>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
+      <c r="B5" s="87" t="s">
+        <v>273</v>
+      </c>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
     </row>
     <row r="6" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72" t="s">
-        <v>284</v>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D7" s="7">
         <v>5784.15</v>
@@ -4932,15 +4984,15 @@
         <v>0.18433129057238734</v>
       </c>
       <c r="H7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D8" s="10">
         <v>7858.35</v>
@@ -4955,10 +5007,10 @@
     </row>
     <row r="9" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" s="7">
         <v>13261.46</v>
@@ -4966,17 +5018,17 @@
       <c r="E9" s="7">
         <v>2276.65</v>
       </c>
-      <c r="F9" s="76">
+      <c r="F9" s="74">
         <f>D9/D11</f>
         <v>0.42262078899649769</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10" s="10">
         <v>4475.1400000000003</v>
@@ -4989,19 +5041,19 @@
         <v>0.14261530764107322</v>
       </c>
       <c r="H10" t="s">
-        <v>278</v>
-      </c>
-      <c r="I10" s="70">
+        <v>275</v>
+      </c>
+      <c r="I10" s="68">
         <f>E10-D10</f>
         <v>12021.170000000002</v>
       </c>
     </row>
     <row r="11" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D11" s="13">
         <f>SUM(D7:D10)</f>
@@ -5016,48 +5068,48 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="85"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
     </row>
     <row r="14" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="89" t="s">
-        <v>279</v>
-      </c>
-      <c r="C14" s="101"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="101"/>
+      <c r="B14" s="87" t="s">
+        <v>276</v>
+      </c>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
     </row>
     <row r="15" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D16" s="7">
         <v>359.79</v>
@@ -5072,10 +5124,10 @@
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D17" s="10">
         <v>19.29</v>
@@ -5088,20 +5140,20 @@
         <v>2.4547137757926279E-3</v>
       </c>
       <c r="H17" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" s="82">
+        <v>101</v>
+      </c>
+      <c r="D18" s="80">
         <v>1001.91</v>
       </c>
-      <c r="E18" s="82">
+      <c r="E18" s="80">
         <v>1144.69</v>
       </c>
       <c r="F18" s="54">
@@ -5111,10 +5163,10 @@
     </row>
     <row r="19" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D19" s="10">
         <v>468.96</v>
@@ -5129,141 +5181,141 @@
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C20" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="79">
+        <v>-688.47</v>
+      </c>
+      <c r="E20" s="79">
+        <v>-487.22</v>
+      </c>
+      <c r="F20" s="78" t="s">
         <v>214</v>
       </c>
-      <c r="C20" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" s="81">
-        <v>-688.47</v>
-      </c>
-      <c r="E20" s="81">
-        <v>-487.22</v>
-      </c>
-      <c r="F20" s="80" t="s">
-        <v>215</v>
-      </c>
       <c r="H20" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" s="78">
+        <v>101</v>
+      </c>
+      <c r="D21" s="76">
         <f>SUM(D16:D20)</f>
         <v>1161.48</v>
       </c>
-      <c r="E21" s="78">
+      <c r="E21" s="76">
         <f>SUM(E16:E20)</f>
         <v>1261.6600000000001</v>
       </c>
-      <c r="F21" s="79" t="s">
-        <v>215</v>
+      <c r="F21" s="77" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="85"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
     </row>
     <row r="24" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="112" t="s">
-        <v>280</v>
-      </c>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="90"/>
+      <c r="B24" s="109" t="s">
+        <v>277</v>
+      </c>
+      <c r="C24" s="88"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="88"/>
     </row>
     <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="101" t="s">
+      <c r="B25" s="98" t="s">
+        <v>216</v>
+      </c>
+      <c r="C25" s="98"/>
+      <c r="D25" s="110" t="s">
         <v>217</v>
       </c>
-      <c r="C25" s="101"/>
-      <c r="D25" s="113" t="s">
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
+      <c r="H25" s="66" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="111" t="s">
         <v>218</v>
       </c>
-      <c r="E25" s="113"/>
-      <c r="F25" s="113"/>
-      <c r="H25" s="68" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="114" t="s">
+      <c r="C26" s="111"/>
+      <c r="D26" s="112" t="s">
         <v>219</v>
       </c>
-      <c r="C26" s="114"/>
-      <c r="D26" s="115" t="s">
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+    </row>
+    <row r="27" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="104" t="s">
         <v>220</v>
       </c>
-      <c r="E26" s="115"/>
-      <c r="F26" s="115"/>
-    </row>
-    <row r="27" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="107" t="s">
+      <c r="C27" s="104"/>
+      <c r="D27" s="105" t="s">
         <v>221</v>
       </c>
-      <c r="C27" s="107"/>
-      <c r="D27" s="108" t="s">
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+    </row>
+    <row r="28" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="106" t="s">
         <v>222</v>
       </c>
-      <c r="E27" s="108"/>
-      <c r="F27" s="108"/>
-    </row>
-    <row r="28" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="109" t="s">
+      <c r="C28" s="106"/>
+      <c r="D28" s="107" t="s">
         <v>223</v>
       </c>
-      <c r="C28" s="109"/>
-      <c r="D28" s="110" t="s">
+      <c r="E28" s="107"/>
+      <c r="F28" s="107"/>
+      <c r="H28" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="104" t="s">
         <v>224</v>
       </c>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
-      <c r="H28" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="107" t="s">
+      <c r="C29" s="104"/>
+      <c r="D29" s="108" t="s">
+        <v>283</v>
+      </c>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+    </row>
+    <row r="30" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="102" t="s">
         <v>225</v>
       </c>
-      <c r="C29" s="107"/>
-      <c r="D29" s="111" t="s">
-        <v>286</v>
-      </c>
-      <c r="E29" s="108"/>
-      <c r="F29" s="108"/>
-    </row>
-    <row r="30" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="105" t="s">
+      <c r="C30" s="102"/>
+      <c r="D30" s="103" t="s">
         <v>226</v>
       </c>
-      <c r="C30" s="105"/>
-      <c r="D30" s="106" t="s">
-        <v>227</v>
-      </c>
-      <c r="E30" s="106"/>
-      <c r="F30" s="106"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="103"/>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
-      <c r="B32" s="85"/>
-      <c r="C32" s="85"/>
-      <c r="D32" s="85"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="85"/>
+      <c r="A32" s="83"/>
+      <c r="B32" s="83"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+      <c r="F32" s="83"/>
+      <c r="G32" s="83"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -5305,103 +5357,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="99" t="s">
-        <v>281</v>
-      </c>
-      <c r="C1" s="100"/>
+      <c r="B1" s="96" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1" s="97"/>
     </row>
     <row r="2" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
     </row>
     <row r="3" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
     </row>
     <row r="5" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="56" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5" s="75" t="s">
         <v>228</v>
-      </c>
-      <c r="C5" s="77" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="57" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" s="58" t="s">
         <v>230</v>
-      </c>
-      <c r="C7" s="58" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="57" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" s="58" t="s">
         <v>232</v>
-      </c>
-      <c r="C9" s="58" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="C11" s="60" t="s">
         <v>234</v>
-      </c>
-      <c r="C11" s="60" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="61" t="s">
+        <v>235</v>
+      </c>
+      <c r="C13" s="62" t="s">
         <v>236</v>
-      </c>
-      <c r="C13" s="62" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="2:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="63" t="s">
+        <v>237</v>
+      </c>
+      <c r="C15" s="64" t="s">
         <v>238</v>
-      </c>
-      <c r="C15" s="64" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="61" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" s="62" t="s">
         <v>240</v>
-      </c>
-      <c r="C17" s="62" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="65" t="s">
-        <v>242</v>
-      </c>
-      <c r="C19" s="66" t="s">
-        <v>243</v>
+      <c r="B19" s="118" t="s">
+        <v>294</v>
+      </c>
+      <c r="C19" s="119" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="103" t="s">
+      <c r="A21" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="103"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="103"/>
+      <c r="B21" s="100"/>
+      <c r="C21" s="100"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="100"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="3">
